--- a/All_Prices.xlsx
+++ b/All_Prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yadmitrieva/EPL Tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C542C88D-1C2F-A04C-AF53-A14854371457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D11D6E-D733-2144-963D-9AC5BE303601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="820" windowWidth="30240" windowHeight="17440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="30240" windowHeight="17440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Admin" sheetId="5" r:id="rId1"/>
@@ -839,125 +839,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="1"/>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1408,6 +1289,125 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="1"/>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1422,27 +1422,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0F118954-90FD-1D49-8627-2A87DB299C4D}" name="T_PriceListsDatabase" displayName="T_PriceListsDatabase" ref="A1:P99" totalsRowShown="0" headerRowDxfId="25">
-  <autoFilter ref="A1:P99" xr:uid="{0F118954-90FD-1D49-8627-2A87DB299C4D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0F118954-90FD-1D49-8627-2A87DB299C4D}" name="T_PriceListsDatabase" displayName="T_PriceListsDatabase" ref="A1:P99" totalsRowShown="0" headerRowDxfId="33">
+  <autoFilter ref="A1:P99" xr:uid="{0F118954-90FD-1D49-8627-2A87DB299C4D}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="V1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{37D2F902-ABD9-4643-A4D7-B5B95F8EB3DD}" name="SAP Plant"/>
-    <tableColumn id="2" xr3:uid="{5B3FAA56-8691-6B45-BE88-1FAD6CD79814}" name="Customer ref. SAP" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{371D5FE5-8C9A-EC43-BDB3-7F3A516D0026}" name="Effective" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{C5A79962-6221-1549-BAB4-FC8C5A183437}" name="Mailing date" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{CD814802-AC17-394B-824B-A91512F11E29}" name="Customer Short Name" dataDxfId="21">
+    <tableColumn id="2" xr3:uid="{5B3FAA56-8691-6B45-BE88-1FAD6CD79814}" name="Customer ref. SAP" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{371D5FE5-8C9A-EC43-BDB3-7F3A516D0026}" name="Effective" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{C5A79962-6221-1549-BAB4-FC8C5A183437}" name="Mailing date" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{CD814802-AC17-394B-824B-A91512F11E29}" name="Customer Short Name" dataDxfId="29">
       <calculatedColumnFormula>_xlfn.XLOOKUP('Prices Database'!B2,'Customers Masterdata'!F:F,'Customers Masterdata'!G:G)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{35843D4F-3CF9-5A45-94C4-C2D637FC48E1}" name="Price List Version" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{D909CC7A-A93A-144B-A2AE-682919516B1F}" name="Comments about Changes" dataDxfId="19"/>
-    <tableColumn id="15" xr3:uid="{803EFC74-00E4-464C-91D8-8542A8D43EC2}" name="Price Type (Discount, Net Price)" dataDxfId="18"/>
-    <tableColumn id="16" xr3:uid="{073928F4-7D0B-BB49-AEE6-06E3D09F786E}" name="If Type Discount - Discount %" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{19E42D72-2648-484B-8CF2-B93EA577FF36}" name="Price List ID" dataDxfId="16">
+    <tableColumn id="6" xr3:uid="{35843D4F-3CF9-5A45-94C4-C2D637FC48E1}" name="Price List Version" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{D909CC7A-A93A-144B-A2AE-682919516B1F}" name="Comments about Changes" dataDxfId="27"/>
+    <tableColumn id="15" xr3:uid="{803EFC74-00E4-464C-91D8-8542A8D43EC2}" name="Price Type (Discount, Net Price)" dataDxfId="26"/>
+    <tableColumn id="16" xr3:uid="{073928F4-7D0B-BB49-AEE6-06E3D09F786E}" name="If Type Discount - Discount %" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{19E42D72-2648-484B-8CF2-B93EA577FF36}" name="Price List ID" dataDxfId="24">
       <calculatedColumnFormula>B2&amp;C2&amp;D2&amp;F2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{4FB4E62E-D1DE-7744-BE1C-C17981BFA9AE}" name="Product type"/>
-    <tableColumn id="10" xr3:uid="{3CA5389E-BE54-514B-BBCB-ECBF466B186F}" name="RIP code" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{3CA5389E-BE54-514B-BBCB-ECBF466B186F}" name="RIP code" dataDxfId="23"/>
     <tableColumn id="11" xr3:uid="{C0411C6D-51D5-4A4F-8872-BC47F7B10E29}" name="Product"/>
-    <tableColumn id="12" xr3:uid="{96C25DB5-B98C-FA40-B263-F9612D0DADE1}" name="Net price_x000a_(Currency / Unit)" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{96C25DB5-B98C-FA40-B263-F9612D0DADE1}" name="Net price_x000a_(Currency / Unit)" dataDxfId="22"/>
     <tableColumn id="13" xr3:uid="{FE678BD4-6DEE-7B47-B7BA-64578B01D1A7}" name="Currency"/>
     <tableColumn id="14" xr3:uid="{18D3A197-DB24-144D-940B-A2D922C84EEA}" name="Unit"/>
   </tableColumns>
@@ -1457,7 +1463,7 @@
     <tableColumn id="1" xr3:uid="{C394DC01-2FA5-F249-8E27-593C8E0CC130}" name="Packagin Version"/>
     <tableColumn id="2" xr3:uid="{235AF419-5F84-8F45-8F40-4227D19A3017}" name="Product Type"/>
     <tableColumn id="4" xr3:uid="{2492B6A6-ECAD-B944-9286-1D10F97121C1}" name="Packaging Name"/>
-    <tableColumn id="5" xr3:uid="{15301E65-3DD2-6D42-98FE-D9684530DE40}" name="Price" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{15301E65-3DD2-6D42-98FE-D9684530DE40}" name="Price" dataDxfId="21"/>
     <tableColumn id="6" xr3:uid="{38E11289-FFED-F242-8D66-3814249EB7CB}" name="Currency"/>
     <tableColumn id="7" xr3:uid="{B03AE9A3-266E-E84E-A2EF-1EC53CADA514}" name="Unit"/>
   </tableColumns>
@@ -1472,7 +1478,7 @@
     <tableColumn id="1" xr3:uid="{548B632C-CB06-6149-BFED-10326A4592F6}" name="Packagin Version"/>
     <tableColumn id="2" xr3:uid="{E7552D57-4470-7049-901C-65B811D82275}" name="Product Type"/>
     <tableColumn id="3" xr3:uid="{EC1D7A85-3113-0345-A020-6F4A505D0616}" name="Packaging Name"/>
-    <tableColumn id="4" xr3:uid="{5EFFAEFC-4F74-0446-844E-7CED7F985D3B}" name="Price" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{5EFFAEFC-4F74-0446-844E-7CED7F985D3B}" name="Price" dataDxfId="20"/>
     <tableColumn id="5" xr3:uid="{A14B6A73-05FD-684E-B7F2-CB1A0E156CAF}" name="Currency"/>
     <tableColumn id="6" xr3:uid="{5E311707-2C84-4840-9044-C36D000DAEC6}" name="Unit"/>
   </tableColumns>
@@ -1481,7 +1487,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{018A20AE-9210-2043-B769-6227B8627523}" name="T_CustomerMasterdata" displayName="T_CustomerMasterdata" ref="A1:T3" totalsRowShown="0" headerRowDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{018A20AE-9210-2043-B769-6227B8627523}" name="T_CustomerMasterdata" displayName="T_CustomerMasterdata" ref="A1:T3" totalsRowShown="0" headerRowDxfId="43">
   <autoFilter ref="A1:T3" xr:uid="{018A20AE-9210-2043-B769-6227B8627523}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{7EB59029-C014-3344-9B1E-D008A6B2DA3B}" name="Zone"/>
@@ -1489,22 +1495,22 @@
     <tableColumn id="3" xr3:uid="{A908BA89-C7CB-6B41-85D5-1C0DF4FB4D46}" name="Customer Type"/>
     <tableColumn id="4" xr3:uid="{B9BDA364-BF2D-F540-BCD6-07DD275210AC}" name="Comment on Business Model"/>
     <tableColumn id="5" xr3:uid="{B88C2814-DEC7-F84F-8661-43580C35894C}" name="Customer ref. type SAP"/>
-    <tableColumn id="6" xr3:uid="{2248B505-D962-1C43-B454-A4B8B178A3A3}" name="Customer ref. SAP" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{0D5F9FD0-FC01-4E48-A7BA-C4855FE9E8DF}" name="Customer Short Name" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{97C47538-7703-A249-BD86-0BB7284A02BA}" name="Customer Full Name" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{2248B505-D962-1C43-B454-A4B8B178A3A3}" name="Customer ref. SAP" dataDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{0D5F9FD0-FC01-4E48-A7BA-C4855FE9E8DF}" name="Customer Short Name" dataDxfId="41"/>
+    <tableColumn id="8" xr3:uid="{97C47538-7703-A249-BD86-0BB7284A02BA}" name="Customer Full Name" dataDxfId="40"/>
     <tableColumn id="9" xr3:uid="{3584453D-FF07-2B42-9C37-5EEDB8A1F9D8}" name="Currency"/>
     <tableColumn id="10" xr3:uid="{2897689C-CFDA-FD43-93C5-8C5944728291}" name="Packagin Version"/>
-    <tableColumn id="11" xr3:uid="{D2EDF6D2-15D0-6747-AC2D-FEF45DEB9429}" name="Pice List Managed by" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{2220F48A-029C-2545-90A3-F30C56C520A6}" name="Customer SPOC" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{E58B7D03-8C98-B549-9F8C-13E8A39B9A7F}" name="Effective" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{61359FB1-0C15-9646-BC4E-8F4924D00884}" name="Mailing date" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{D2EDF6D2-15D0-6747-AC2D-FEF45DEB9429}" name="Pice List Managed by" dataDxfId="39"/>
+    <tableColumn id="12" xr3:uid="{2220F48A-029C-2545-90A3-F30C56C520A6}" name="Customer SPOC" dataDxfId="38"/>
+    <tableColumn id="13" xr3:uid="{E58B7D03-8C98-B549-9F8C-13E8A39B9A7F}" name="Effective" dataDxfId="37"/>
+    <tableColumn id="14" xr3:uid="{61359FB1-0C15-9646-BC4E-8F4924D00884}" name="Mailing date" dataDxfId="36"/>
     <tableColumn id="15" xr3:uid="{FAD338F2-73B5-D14D-A9DA-8A2B14C800D0}" name="Last Price List Version"/>
-    <tableColumn id="20" xr3:uid="{187403D4-6469-DC45-BA9B-16EA70F7835F}" name="Last Price List ID" dataDxfId="3">
+    <tableColumn id="20" xr3:uid="{187403D4-6469-DC45-BA9B-16EA70F7835F}" name="Last Price List ID" dataDxfId="35">
       <calculatedColumnFormula>T_CustomerMasterdata[[#This Row],[Customer ref. SAP]]&amp;T_CustomerMasterdata[[#This Row],[Effective]]&amp;T_CustomerMasterdata[[#This Row],[Mailing date]]&amp;T_CustomerMasterdata[[#This Row],[Last Price List Version]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{EC332BF1-4B64-5B43-BC9E-F79444DCF47A}" name="Mailing TO: Customer"/>
     <tableColumn id="17" xr3:uid="{9EBF1ECC-3E2A-3946-BB40-511666ABEA7E}" name="Internal COPY: SPOC + RZM + Other"/>
-    <tableColumn id="18" xr3:uid="{BA8B7E30-778E-CF43-8DDD-8E78FEC4DA23}" name="Internal COPY to: PBP (Costing manager)" dataDxfId="2" dataCellStyle="Hyperlink">
+    <tableColumn id="18" xr3:uid="{BA8B7E30-778E-CF43-8DDD-8E78FEC4DA23}" name="Internal COPY to: PBP (Costing manager)" dataDxfId="34" dataCellStyle="Hyperlink">
       <calculatedColumnFormula>V_Email_PBPCostingManager</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="19" xr3:uid="{4AC3D85B-5286-AD4D-A8BF-16A422922E85}" name="COPY to: PBP common mail box"/>
@@ -1514,30 +1520,30 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{08583D75-F5E0-9247-8420-043E947DF895}" name="Table_StandardEPL_USD" displayName="Table_StandardEPL_USD" ref="A1:F46" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42" tableBorderDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{08583D75-F5E0-9247-8420-043E947DF895}" name="Table_StandardEPL_USD" displayName="Table_StandardEPL_USD" ref="A1:F46" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18" tableBorderDxfId="17">
   <autoFilter ref="A1:F46" xr:uid="{08583D75-F5E0-9247-8420-043E947DF895}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{D5370C0F-EF1F-FE4E-823B-BC12FBF5E1D8}" name="Product type" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{AFD818D7-01BD-EA47-8510-CE3DB782DEF7}" name="RIP code" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{BA1D3757-D246-9A40-95A5-59035BC3596B}" name="Product" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{19A22FA5-1301-2048-A200-D2786122F32C}" name="Net price_x000a_(Currency / Unit)" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{3D9EC9B7-AFFB-064C-8969-D35D91D4911A}" name="Currency" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{132A2678-6F02-3B48-A3D3-9A7A1715C7E3}" name="Unit" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{D5370C0F-EF1F-FE4E-823B-BC12FBF5E1D8}" name="Product type" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{AFD818D7-01BD-EA47-8510-CE3DB782DEF7}" name="RIP code" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{BA1D3757-D246-9A40-95A5-59035BC3596B}" name="Product" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{19A22FA5-1301-2048-A200-D2786122F32C}" name="Net price_x000a_(Currency / Unit)" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{3D9EC9B7-AFFB-064C-8969-D35D91D4911A}" name="Currency" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{132A2678-6F02-3B48-A3D3-9A7A1715C7E3}" name="Unit" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C9FDDAA2-BE48-784E-9ADE-65BB176C5DFA}" name="Table_StandardEPL_EUR" displayName="Table_StandardEPL_EUR" ref="I1:N12" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33" tableBorderDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C9FDDAA2-BE48-784E-9ADE-65BB176C5DFA}" name="Table_StandardEPL_EUR" displayName="Table_StandardEPL_EUR" ref="I1:N12" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" tableBorderDxfId="8">
   <autoFilter ref="I1:N12" xr:uid="{C9FDDAA2-BE48-784E-9ADE-65BB176C5DFA}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{E5F45572-BC3D-E84C-819A-8A61994AFC61}" name="Product type" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{2464CE3D-2F29-3641-80B9-F388FE026E6C}" name="RIP code" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{B9359043-9086-8F4B-AED6-7C5C27FB0A7D}" name="Product" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{8658424D-4B49-EA49-82C4-7494A9E30DA0}" name="Net price_x000a_(Currency / Unit)" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{A439F0F3-48F3-5B4B-A620-C67704060E10}" name="Currency" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{7F65394B-ED7C-6148-B52C-C9B1DADA10E5}" name="Unit" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{E5F45572-BC3D-E84C-819A-8A61994AFC61}" name="Product type" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{2464CE3D-2F29-3641-80B9-F388FE026E6C}" name="RIP code" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{B9359043-9086-8F4B-AED6-7C5C27FB0A7D}" name="Product" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{8658424D-4B49-EA49-82C4-7494A9E30DA0}" name="Net price_x000a_(Currency / Unit)" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{A439F0F3-48F3-5B4B-A620-C67704060E10}" name="Currency" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{7F65394B-ED7C-6148-B52C-C9B1DADA10E5}" name="Unit" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3949,10 +3955,10 @@
         <v>58</v>
       </c>
       <c r="C43" s="19">
-        <v>45444</v>
+        <v>36527</v>
       </c>
       <c r="D43" s="19">
-        <v>45454</v>
+        <v>36526</v>
       </c>
       <c r="E43" s="5" t="str">
         <f>_xlfn.XLOOKUP('Prices Database'!B43,'Customers Masterdata'!F:F,'Customers Masterdata'!G:G)</f>
@@ -3972,7 +3978,7 @@
       </c>
       <c r="J43" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>XXXXX14544445454V1</v>
+        <v>XXXXX13652736526V1</v>
       </c>
       <c r="K43" t="s">
         <v>14</v>
@@ -3993,7 +3999,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>165</v>
       </c>
@@ -4045,7 +4051,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>165</v>
       </c>
@@ -4097,7 +4103,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B46" s="3" t="s">
         <v>58</v>
       </c>
@@ -4146,7 +4152,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B47" s="3" t="s">
         <v>58</v>
       </c>
@@ -4195,7 +4201,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B48" s="3" t="s">
         <v>58</v>
       </c>
@@ -4244,7 +4250,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B49" s="3" t="s">
         <v>58</v>
       </c>
@@ -4293,7 +4299,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B50" s="3" t="s">
         <v>58</v>
       </c>
@@ -4342,7 +4348,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B51" s="3" t="s">
         <v>58</v>
       </c>
@@ -4391,7 +4397,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B52" s="3" t="s">
         <v>58</v>
       </c>
@@ -4440,7 +4446,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B53" s="3" t="s">
         <v>58</v>
       </c>
@@ -4489,7 +4495,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B54" s="3" t="s">
         <v>58</v>
       </c>
@@ -4538,7 +4544,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B55" s="3" t="s">
         <v>58</v>
       </c>
@@ -4587,7 +4593,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B56" s="3" t="s">
         <v>58</v>
       </c>
@@ -4636,7 +4642,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B57" s="3" t="s">
         <v>58</v>
       </c>
@@ -4685,7 +4691,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B58" s="3" t="s">
         <v>58</v>
       </c>
@@ -4734,7 +4740,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B59" s="3" t="s">
         <v>58</v>
       </c>
@@ -4783,7 +4789,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B60" s="3" t="s">
         <v>58</v>
       </c>
@@ -4832,7 +4838,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B61" s="3" t="s">
         <v>58</v>
       </c>
@@ -4881,7 +4887,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B62" s="3" t="s">
         <v>58</v>
       </c>
@@ -4930,7 +4936,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B63" s="3" t="s">
         <v>58</v>
       </c>
@@ -4979,7 +4985,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B64" s="3" t="s">
         <v>58</v>
       </c>
@@ -5028,7 +5034,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B65" s="3" t="s">
         <v>58</v>
       </c>
@@ -5077,7 +5083,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B66" s="3" t="s">
         <v>58</v>
       </c>
@@ -5126,7 +5132,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B67" s="3" t="s">
         <v>58</v>
       </c>
@@ -5175,7 +5181,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B68" s="3" t="s">
         <v>58</v>
       </c>
@@ -5224,7 +5230,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B69" s="3" t="s">
         <v>58</v>
       </c>
@@ -5273,7 +5279,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B70" s="3" t="s">
         <v>58</v>
       </c>
@@ -5322,7 +5328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B71" s="3" t="s">
         <v>58</v>
       </c>
@@ -5371,7 +5377,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B72" s="3" t="s">
         <v>58</v>
       </c>
@@ -5420,7 +5426,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B73" s="3" t="s">
         <v>58</v>
       </c>
@@ -5469,7 +5475,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B74" s="3" t="s">
         <v>58</v>
       </c>
@@ -5518,7 +5524,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B75" s="3" t="s">
         <v>58</v>
       </c>
@@ -5567,7 +5573,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B76" s="3" t="s">
         <v>58</v>
       </c>
@@ -5616,7 +5622,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B77" s="3" t="s">
         <v>58</v>
       </c>
@@ -5665,7 +5671,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B78" s="3" t="s">
         <v>58</v>
       </c>
@@ -5714,7 +5720,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B79" s="3" t="s">
         <v>58</v>
       </c>
@@ -5763,7 +5769,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B80" s="3" t="s">
         <v>58</v>
       </c>
@@ -5812,7 +5818,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B81" s="3" t="s">
         <v>58</v>
       </c>
@@ -5861,7 +5867,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B82" s="3" t="s">
         <v>58</v>
       </c>
@@ -5910,7 +5916,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B83" s="3" t="s">
         <v>58</v>
       </c>
@@ -5959,7 +5965,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B84" s="3" t="s">
         <v>58</v>
       </c>
@@ -6008,7 +6014,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B85" s="3" t="s">
         <v>58</v>
       </c>
@@ -6057,7 +6063,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B86" s="3" t="s">
         <v>58</v>
       </c>
@@ -6106,7 +6112,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B87" s="3" t="s">
         <v>58</v>
       </c>
@@ -6155,7 +6161,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B88" s="3" t="s">
         <v>58</v>
       </c>
@@ -13437,12 +13443,36 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <DOC_TYPE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <REF_YEAR__x002f__ANNEE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">2023</REF_YEAR__x002f__ANNEE>
+    <PERIOD xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <DEPT_AUTOR xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <TARGET_AUDIENCE__x002f__DESTINATAIRE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <DOC_STATUS xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">Update Version/Version Actuelle</DOC_STATUS>
+    <Remark xmlns="7e83e573-fb93-452c-9f3b-7b87af48cc96" xsi:nil="true"/>
+    <DOC_LANGUAGE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">
+      <Value>French (France)</Value>
+    </DOC_LANGUAGE>
+    <MARKET__x002f__MARCHE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <TAG_2 xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <PRODUCT__x002f__RANGE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">
+      <Value>-</Value>
+    </PRODUCT__x002f__RANGE>
+    <IDENTIFICATION_REFERENCE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <DOMAIN xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <DOC_DESCRIPTION xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e83e573-fb93-452c-9f3b-7b87af48cc96">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <TAG_1 xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17130,42 +17160,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <DOC_TYPE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <REF_YEAR__x002f__ANNEE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">2023</REF_YEAR__x002f__ANNEE>
-    <PERIOD xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <DEPT_AUTOR xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <TARGET_AUDIENCE__x002f__DESTINATAIRE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <DOC_STATUS xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">Update Version/Version Actuelle</DOC_STATUS>
-    <Remark xmlns="7e83e573-fb93-452c-9f3b-7b87af48cc96" xsi:nil="true"/>
-    <DOC_LANGUAGE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">
-      <Value>French (France)</Value>
-    </DOC_LANGUAGE>
-    <MARKET__x002f__MARCHE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <TAG_2 xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <PRODUCT__x002f__RANGE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">
-      <Value>-</Value>
-    </PRODUCT__x002f__RANGE>
-    <IDENTIFICATION_REFERENCE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <DOMAIN xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <DOC_DESCRIPTION xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e83e573-fb93-452c-9f3b-7b87af48cc96">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <TAG_1 xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08C24CE9-94B3-4210-8D15-1D41A580968E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F55DE33-C1A5-4F20-B814-5EC50C36FAFB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dc163805-5a8a-4bac-b0c0-60a9bfcd087a"/>
+    <ds:schemaRef ds:uri="7e83e573-fb93-452c-9f3b-7b87af48cc96"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17190,12 +17199,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F55DE33-C1A5-4F20-B814-5EC50C36FAFB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08C24CE9-94B3-4210-8D15-1D41A580968E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dc163805-5a8a-4bac-b0c0-60a9bfcd087a"/>
-    <ds:schemaRef ds:uri="7e83e573-fb93-452c-9f3b-7b87af48cc96"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/All_Prices.xlsx
+++ b/All_Prices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yadmitrieva/EPL Tool/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dmitr\OneDrive\Documents\() Dev\EPL-Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D11D6E-D733-2144-963D-9AC5BE303601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2646B75-19A5-488E-9CBB-BB5527B8D69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="30240" windowHeight="17440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Admin" sheetId="5" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="186">
   <si>
     <t>Product type</t>
   </si>
@@ -604,14 +604,30 @@
   <si>
     <t>Internal COPY to: PBP (Costing manager)</t>
   </si>
+  <si>
+    <t>XXXXX3</t>
+  </si>
+  <si>
+    <t>Cust GBP</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>GBP-Standard</t>
+  </si>
+  <si>
+    <t>Customer GBP</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="166" formatCode="m/d/yy"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -708,7 +724,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -740,13 +756,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -805,6 +830,20 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1290,6 +1329,59 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="m/d/yy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="m/d/yy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="1"/>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1355,59 +1447,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="1"/>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1422,33 +1461,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0F118954-90FD-1D49-8627-2A87DB299C4D}" name="T_PriceListsDatabase" displayName="T_PriceListsDatabase" ref="A1:P99" totalsRowShown="0" headerRowDxfId="33">
-  <autoFilter ref="A1:P99" xr:uid="{0F118954-90FD-1D49-8627-2A87DB299C4D}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="V1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0F118954-90FD-1D49-8627-2A87DB299C4D}" name="T_PriceListsDatabase" displayName="T_PriceListsDatabase" ref="A1:P99" totalsRowShown="0" headerRowDxfId="43">
+  <autoFilter ref="A1:P99" xr:uid="{0F118954-90FD-1D49-8627-2A87DB299C4D}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{37D2F902-ABD9-4643-A4D7-B5B95F8EB3DD}" name="SAP Plant"/>
-    <tableColumn id="2" xr3:uid="{5B3FAA56-8691-6B45-BE88-1FAD6CD79814}" name="Customer ref. SAP" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{371D5FE5-8C9A-EC43-BDB3-7F3A516D0026}" name="Effective" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{C5A79962-6221-1549-BAB4-FC8C5A183437}" name="Mailing date" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{CD814802-AC17-394B-824B-A91512F11E29}" name="Customer Short Name" dataDxfId="29">
+    <tableColumn id="2" xr3:uid="{5B3FAA56-8691-6B45-BE88-1FAD6CD79814}" name="Customer ref. SAP" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{371D5FE5-8C9A-EC43-BDB3-7F3A516D0026}" name="Effective" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{C5A79962-6221-1549-BAB4-FC8C5A183437}" name="Mailing date" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{CD814802-AC17-394B-824B-A91512F11E29}" name="Customer Short Name" dataDxfId="39">
       <calculatedColumnFormula>_xlfn.XLOOKUP('Prices Database'!B2,'Customers Masterdata'!F:F,'Customers Masterdata'!G:G)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{35843D4F-3CF9-5A45-94C4-C2D637FC48E1}" name="Price List Version" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{D909CC7A-A93A-144B-A2AE-682919516B1F}" name="Comments about Changes" dataDxfId="27"/>
-    <tableColumn id="15" xr3:uid="{803EFC74-00E4-464C-91D8-8542A8D43EC2}" name="Price Type (Discount, Net Price)" dataDxfId="26"/>
-    <tableColumn id="16" xr3:uid="{073928F4-7D0B-BB49-AEE6-06E3D09F786E}" name="If Type Discount - Discount %" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{19E42D72-2648-484B-8CF2-B93EA577FF36}" name="Price List ID" dataDxfId="24">
+    <tableColumn id="6" xr3:uid="{35843D4F-3CF9-5A45-94C4-C2D637FC48E1}" name="Price List Version" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{D909CC7A-A93A-144B-A2AE-682919516B1F}" name="Comments about Changes" dataDxfId="37"/>
+    <tableColumn id="15" xr3:uid="{803EFC74-00E4-464C-91D8-8542A8D43EC2}" name="Price Type (Discount, Net Price)" dataDxfId="36"/>
+    <tableColumn id="16" xr3:uid="{073928F4-7D0B-BB49-AEE6-06E3D09F786E}" name="If Type Discount - Discount %" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{19E42D72-2648-484B-8CF2-B93EA577FF36}" name="Price List ID" dataDxfId="34">
       <calculatedColumnFormula>B2&amp;C2&amp;D2&amp;F2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{4FB4E62E-D1DE-7744-BE1C-C17981BFA9AE}" name="Product type"/>
-    <tableColumn id="10" xr3:uid="{3CA5389E-BE54-514B-BBCB-ECBF466B186F}" name="RIP code" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{3CA5389E-BE54-514B-BBCB-ECBF466B186F}" name="RIP code" dataDxfId="33"/>
     <tableColumn id="11" xr3:uid="{C0411C6D-51D5-4A4F-8872-BC47F7B10E29}" name="Product"/>
-    <tableColumn id="12" xr3:uid="{96C25DB5-B98C-FA40-B263-F9612D0DADE1}" name="Net price_x000a_(Currency / Unit)" dataDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{96C25DB5-B98C-FA40-B263-F9612D0DADE1}" name="Net price_x000a_(Currency / Unit)" dataDxfId="32"/>
     <tableColumn id="13" xr3:uid="{FE678BD4-6DEE-7B47-B7BA-64578B01D1A7}" name="Currency"/>
     <tableColumn id="14" xr3:uid="{18D3A197-DB24-144D-940B-A2D922C84EEA}" name="Unit"/>
   </tableColumns>
@@ -1463,7 +1496,7 @@
     <tableColumn id="1" xr3:uid="{C394DC01-2FA5-F249-8E27-593C8E0CC130}" name="Packagin Version"/>
     <tableColumn id="2" xr3:uid="{235AF419-5F84-8F45-8F40-4227D19A3017}" name="Product Type"/>
     <tableColumn id="4" xr3:uid="{2492B6A6-ECAD-B944-9286-1D10F97121C1}" name="Packaging Name"/>
-    <tableColumn id="5" xr3:uid="{15301E65-3DD2-6D42-98FE-D9684530DE40}" name="Price" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{15301E65-3DD2-6D42-98FE-D9684530DE40}" name="Price" dataDxfId="31"/>
     <tableColumn id="6" xr3:uid="{38E11289-FFED-F242-8D66-3814249EB7CB}" name="Currency"/>
     <tableColumn id="7" xr3:uid="{B03AE9A3-266E-E84E-A2EF-1EC53CADA514}" name="Unit"/>
   </tableColumns>
@@ -1478,7 +1511,7 @@
     <tableColumn id="1" xr3:uid="{548B632C-CB06-6149-BFED-10326A4592F6}" name="Packagin Version"/>
     <tableColumn id="2" xr3:uid="{E7552D57-4470-7049-901C-65B811D82275}" name="Product Type"/>
     <tableColumn id="3" xr3:uid="{EC1D7A85-3113-0345-A020-6F4A505D0616}" name="Packaging Name"/>
-    <tableColumn id="4" xr3:uid="{5EFFAEFC-4F74-0446-844E-7CED7F985D3B}" name="Price" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{5EFFAEFC-4F74-0446-844E-7CED7F985D3B}" name="Price" dataDxfId="30"/>
     <tableColumn id="5" xr3:uid="{A14B6A73-05FD-684E-B7F2-CB1A0E156CAF}" name="Currency"/>
     <tableColumn id="6" xr3:uid="{5E311707-2C84-4840-9044-C36D000DAEC6}" name="Unit"/>
   </tableColumns>
@@ -1487,30 +1520,30 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{018A20AE-9210-2043-B769-6227B8627523}" name="T_CustomerMasterdata" displayName="T_CustomerMasterdata" ref="A1:T3" totalsRowShown="0" headerRowDxfId="43">
-  <autoFilter ref="A1:T3" xr:uid="{018A20AE-9210-2043-B769-6227B8627523}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{018A20AE-9210-2043-B769-6227B8627523}" name="T_CustomerMasterdata" displayName="T_CustomerMasterdata" ref="A1:T4" totalsRowShown="0" headerRowDxfId="29">
+  <autoFilter ref="A1:T4" xr:uid="{018A20AE-9210-2043-B769-6227B8627523}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{7EB59029-C014-3344-9B1E-D008A6B2DA3B}" name="Zone"/>
     <tableColumn id="2" xr3:uid="{C46E54AC-4AB2-3B4A-B621-1D19BD233320}" name="Country"/>
     <tableColumn id="3" xr3:uid="{A908BA89-C7CB-6B41-85D5-1C0DF4FB4D46}" name="Customer Type"/>
     <tableColumn id="4" xr3:uid="{B9BDA364-BF2D-F540-BCD6-07DD275210AC}" name="Comment on Business Model"/>
     <tableColumn id="5" xr3:uid="{B88C2814-DEC7-F84F-8661-43580C35894C}" name="Customer ref. type SAP"/>
-    <tableColumn id="6" xr3:uid="{2248B505-D962-1C43-B454-A4B8B178A3A3}" name="Customer ref. SAP" dataDxfId="42"/>
-    <tableColumn id="7" xr3:uid="{0D5F9FD0-FC01-4E48-A7BA-C4855FE9E8DF}" name="Customer Short Name" dataDxfId="41"/>
-    <tableColumn id="8" xr3:uid="{97C47538-7703-A249-BD86-0BB7284A02BA}" name="Customer Full Name" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{2248B505-D962-1C43-B454-A4B8B178A3A3}" name="Customer ref. SAP" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{0D5F9FD0-FC01-4E48-A7BA-C4855FE9E8DF}" name="Customer Short Name" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{97C47538-7703-A249-BD86-0BB7284A02BA}" name="Customer Full Name" dataDxfId="26"/>
     <tableColumn id="9" xr3:uid="{3584453D-FF07-2B42-9C37-5EEDB8A1F9D8}" name="Currency"/>
     <tableColumn id="10" xr3:uid="{2897689C-CFDA-FD43-93C5-8C5944728291}" name="Packagin Version"/>
-    <tableColumn id="11" xr3:uid="{D2EDF6D2-15D0-6747-AC2D-FEF45DEB9429}" name="Pice List Managed by" dataDxfId="39"/>
-    <tableColumn id="12" xr3:uid="{2220F48A-029C-2545-90A3-F30C56C520A6}" name="Customer SPOC" dataDxfId="38"/>
-    <tableColumn id="13" xr3:uid="{E58B7D03-8C98-B549-9F8C-13E8A39B9A7F}" name="Effective" dataDxfId="37"/>
-    <tableColumn id="14" xr3:uid="{61359FB1-0C15-9646-BC4E-8F4924D00884}" name="Mailing date" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{D2EDF6D2-15D0-6747-AC2D-FEF45DEB9429}" name="Pice List Managed by" dataDxfId="25"/>
+    <tableColumn id="12" xr3:uid="{2220F48A-029C-2545-90A3-F30C56C520A6}" name="Customer SPOC" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{E58B7D03-8C98-B549-9F8C-13E8A39B9A7F}" name="Effective" dataDxfId="23"/>
+    <tableColumn id="14" xr3:uid="{61359FB1-0C15-9646-BC4E-8F4924D00884}" name="Mailing date" dataDxfId="22"/>
     <tableColumn id="15" xr3:uid="{FAD338F2-73B5-D14D-A9DA-8A2B14C800D0}" name="Last Price List Version"/>
-    <tableColumn id="20" xr3:uid="{187403D4-6469-DC45-BA9B-16EA70F7835F}" name="Last Price List ID" dataDxfId="35">
+    <tableColumn id="20" xr3:uid="{187403D4-6469-DC45-BA9B-16EA70F7835F}" name="Last Price List ID" dataDxfId="21">
       <calculatedColumnFormula>T_CustomerMasterdata[[#This Row],[Customer ref. SAP]]&amp;T_CustomerMasterdata[[#This Row],[Effective]]&amp;T_CustomerMasterdata[[#This Row],[Mailing date]]&amp;T_CustomerMasterdata[[#This Row],[Last Price List Version]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{EC332BF1-4B64-5B43-BC9E-F79444DCF47A}" name="Mailing TO: Customer"/>
     <tableColumn id="17" xr3:uid="{9EBF1ECC-3E2A-3946-BB40-511666ABEA7E}" name="Internal COPY: SPOC + RZM + Other"/>
-    <tableColumn id="18" xr3:uid="{BA8B7E30-778E-CF43-8DDD-8E78FEC4DA23}" name="Internal COPY to: PBP (Costing manager)" dataDxfId="34" dataCellStyle="Hyperlink">
+    <tableColumn id="18" xr3:uid="{BA8B7E30-778E-CF43-8DDD-8E78FEC4DA23}" name="Internal COPY to: PBP (Costing manager)" dataDxfId="20" dataCellStyle="Hyperlink">
       <calculatedColumnFormula>V_Email_PBPCostingManager</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="19" xr3:uid="{4AC3D85B-5286-AD4D-A8BF-16A422922E85}" name="COPY to: PBP common mail box"/>
@@ -1826,12 +1859,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABD40FF5-5EC2-D542-B693-2624057EED4C}">
   <dimension ref="B4:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="39.1640625" customWidth="1"/>
+    <col min="3" max="3" width="39.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>171</v>
       </c>
@@ -1839,7 +1872,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>169</v>
       </c>
@@ -1847,7 +1880,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>168</v>
       </c>
@@ -1868,24 +1901,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:Q992"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="17.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="48.33203125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" style="3" customWidth="1"/>
-    <col min="7" max="10" width="30.5" style="5" customWidth="1"/>
-    <col min="11" max="11" width="26.6640625" customWidth="1"/>
-    <col min="12" max="12" width="17.83203125" customWidth="1"/>
-    <col min="13" max="13" width="49.1640625" customWidth="1"/>
-    <col min="14" max="14" width="20.1640625" customWidth="1"/>
-    <col min="15" max="15" width="13.5" customWidth="1"/>
-    <col min="16" max="16" width="15.5" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="48.28515625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" style="3" customWidth="1"/>
+    <col min="7" max="10" width="30.42578125" style="5" customWidth="1"/>
+    <col min="11" max="11" width="26.7109375" customWidth="1"/>
+    <col min="12" max="12" width="17.85546875" customWidth="1"/>
+    <col min="13" max="13" width="49.140625" customWidth="1"/>
+    <col min="14" max="14" width="20.140625" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" customWidth="1"/>
+    <col min="16" max="16" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>50</v>
       </c>
@@ -1935,7 +1968,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>165</v>
       </c>
@@ -1987,7 +2020,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>165</v>
       </c>
@@ -2039,7 +2072,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>58</v>
       </c>
@@ -2088,7 +2121,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>58</v>
       </c>
@@ -2137,7 +2170,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>58</v>
       </c>
@@ -2186,7 +2219,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>58</v>
       </c>
@@ -2235,7 +2268,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>58</v>
       </c>
@@ -2284,7 +2317,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>58</v>
       </c>
@@ -2333,7 +2366,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>58</v>
       </c>
@@ -2382,7 +2415,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>58</v>
       </c>
@@ -2431,7 +2464,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>58</v>
       </c>
@@ -2480,7 +2513,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>58</v>
       </c>
@@ -2529,7 +2562,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>58</v>
       </c>
@@ -2578,7 +2611,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>58</v>
       </c>
@@ -2627,7 +2660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>58</v>
       </c>
@@ -2676,7 +2709,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>58</v>
       </c>
@@ -2725,7 +2758,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>58</v>
       </c>
@@ -2774,7 +2807,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>58</v>
       </c>
@@ -2823,7 +2856,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>58</v>
       </c>
@@ -2872,7 +2905,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>58</v>
       </c>
@@ -2921,7 +2954,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
         <v>58</v>
       </c>
@@ -2970,7 +3003,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
         <v>58</v>
       </c>
@@ -3019,7 +3052,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
         <v>58</v>
       </c>
@@ -3068,7 +3101,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
         <v>58</v>
       </c>
@@ -3117,7 +3150,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
         <v>58</v>
       </c>
@@ -3166,7 +3199,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
         <v>58</v>
       </c>
@@ -3215,7 +3248,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
         <v>58</v>
       </c>
@@ -3264,7 +3297,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
         <v>58</v>
       </c>
@@ -3313,7 +3346,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
         <v>58</v>
       </c>
@@ -3362,7 +3395,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
         <v>58</v>
       </c>
@@ -3411,7 +3444,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
         <v>58</v>
       </c>
@@ -3460,7 +3493,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
         <v>58</v>
       </c>
@@ -3509,7 +3542,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
         <v>58</v>
       </c>
@@ -3558,7 +3591,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
         <v>58</v>
       </c>
@@ -3607,7 +3640,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
         <v>58</v>
       </c>
@@ -3656,7 +3689,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
         <v>58</v>
       </c>
@@ -3705,7 +3738,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B38" s="3" t="s">
         <v>58</v>
       </c>
@@ -3754,7 +3787,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B39" s="3" t="s">
         <v>58</v>
       </c>
@@ -3803,7 +3836,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
         <v>58</v>
       </c>
@@ -3852,7 +3885,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B41" s="3" t="s">
         <v>58</v>
       </c>
@@ -3901,7 +3934,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B42" s="3" t="s">
         <v>58</v>
       </c>
@@ -3950,7 +3983,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B43" s="3" t="s">
         <v>58</v>
       </c>
@@ -3999,7 +4032,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>165</v>
       </c>
@@ -4051,7 +4084,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>165</v>
       </c>
@@ -4103,7 +4136,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
         <v>58</v>
       </c>
@@ -4152,7 +4185,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B47" s="3" t="s">
         <v>58</v>
       </c>
@@ -4201,7 +4234,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B48" s="3" t="s">
         <v>58</v>
       </c>
@@ -4250,7 +4283,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B49" s="3" t="s">
         <v>58</v>
       </c>
@@ -4299,7 +4332,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B50" s="3" t="s">
         <v>58</v>
       </c>
@@ -4348,7 +4381,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B51" s="3" t="s">
         <v>58</v>
       </c>
@@ -4397,7 +4430,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B52" s="3" t="s">
         <v>58</v>
       </c>
@@ -4446,7 +4479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B53" s="3" t="s">
         <v>58</v>
       </c>
@@ -4495,7 +4528,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B54" s="3" t="s">
         <v>58</v>
       </c>
@@ -4544,7 +4577,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B55" s="3" t="s">
         <v>58</v>
       </c>
@@ -4593,7 +4626,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B56" s="3" t="s">
         <v>58</v>
       </c>
@@ -4642,7 +4675,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B57" s="3" t="s">
         <v>58</v>
       </c>
@@ -4691,7 +4724,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B58" s="3" t="s">
         <v>58</v>
       </c>
@@ -4740,7 +4773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B59" s="3" t="s">
         <v>58</v>
       </c>
@@ -4789,7 +4822,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B60" s="3" t="s">
         <v>58</v>
       </c>
@@ -4838,7 +4871,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B61" s="3" t="s">
         <v>58</v>
       </c>
@@ -4887,7 +4920,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B62" s="3" t="s">
         <v>58</v>
       </c>
@@ -4936,7 +4969,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B63" s="3" t="s">
         <v>58</v>
       </c>
@@ -4985,7 +5018,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B64" s="3" t="s">
         <v>58</v>
       </c>
@@ -5034,7 +5067,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B65" s="3" t="s">
         <v>58</v>
       </c>
@@ -5083,7 +5116,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B66" s="3" t="s">
         <v>58</v>
       </c>
@@ -5132,7 +5165,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B67" s="3" t="s">
         <v>58</v>
       </c>
@@ -5181,7 +5214,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B68" s="3" t="s">
         <v>58</v>
       </c>
@@ -5230,7 +5263,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B69" s="3" t="s">
         <v>58</v>
       </c>
@@ -5279,7 +5312,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B70" s="3" t="s">
         <v>58</v>
       </c>
@@ -5328,7 +5361,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B71" s="3" t="s">
         <v>58</v>
       </c>
@@ -5377,7 +5410,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B72" s="3" t="s">
         <v>58</v>
       </c>
@@ -5426,7 +5459,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B73" s="3" t="s">
         <v>58</v>
       </c>
@@ -5475,7 +5508,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B74" s="3" t="s">
         <v>58</v>
       </c>
@@ -5524,7 +5557,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B75" s="3" t="s">
         <v>58</v>
       </c>
@@ -5573,7 +5606,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B76" s="3" t="s">
         <v>58</v>
       </c>
@@ -5622,7 +5655,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B77" s="3" t="s">
         <v>58</v>
       </c>
@@ -5671,7 +5704,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B78" s="3" t="s">
         <v>58</v>
       </c>
@@ -5720,7 +5753,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B79" s="3" t="s">
         <v>58</v>
       </c>
@@ -5769,7 +5802,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B80" s="3" t="s">
         <v>58</v>
       </c>
@@ -5818,7 +5851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B81" s="3" t="s">
         <v>58</v>
       </c>
@@ -5867,7 +5900,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B82" s="3" t="s">
         <v>58</v>
       </c>
@@ -5916,7 +5949,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B83" s="3" t="s">
         <v>58</v>
       </c>
@@ -5965,7 +5998,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B84" s="3" t="s">
         <v>58</v>
       </c>
@@ -6014,7 +6047,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B85" s="3" t="s">
         <v>58</v>
       </c>
@@ -6063,7 +6096,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B86" s="3" t="s">
         <v>58</v>
       </c>
@@ -6112,7 +6145,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B87" s="3" t="s">
         <v>58</v>
       </c>
@@ -6161,7 +6194,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="2:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B88" s="3" t="s">
         <v>58</v>
       </c>
@@ -6210,7 +6243,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B89" s="3" t="s">
         <v>59</v>
       </c>
@@ -6259,7 +6292,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="90" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B90" s="3" t="s">
         <v>59</v>
       </c>
@@ -6308,7 +6341,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B91" s="3" t="s">
         <v>59</v>
       </c>
@@ -6357,7 +6390,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="92" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B92" s="3" t="s">
         <v>59</v>
       </c>
@@ -6406,7 +6439,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="93" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B93" s="3" t="s">
         <v>59</v>
       </c>
@@ -6455,7 +6488,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B94" s="3" t="s">
         <v>59</v>
       </c>
@@ -6504,7 +6537,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B95" s="3" t="s">
         <v>59</v>
       </c>
@@ -6553,7 +6586,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="96" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B96" s="3" t="s">
         <v>59</v>
       </c>
@@ -6602,7 +6635,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="97" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B97" s="3" t="s">
         <v>59</v>
       </c>
@@ -6651,7 +6684,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="98" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B98" s="3" t="s">
         <v>59</v>
       </c>
@@ -6700,7 +6733,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B99" s="3" t="s">
         <v>59</v>
       </c>
@@ -6749,4355 +6782,4398 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="N100" s="6"/>
-      <c r="Q100" s="6"/>
-    </row>
-    <row r="101" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B100" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C100" s="19">
+        <v>45658</v>
+      </c>
+      <c r="D100" s="19">
+        <v>45658</v>
+      </c>
+      <c r="E100" s="5" t="str">
+        <f>_xlfn.XLOOKUP('Prices Database'!B100,'Customers Masterdata'!F:F,'Customers Masterdata'!G:G)</f>
+        <v>Cust GBP</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="I100" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="J100" s="5" t="str">
+        <f t="shared" ref="J100" si="3">B100&amp;C100&amp;D100&amp;F100</f>
+        <v>XXXXX34565845658V1</v>
+      </c>
+      <c r="K100" t="s">
+        <v>11</v>
+      </c>
+      <c r="L100" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="M100" t="s">
+        <v>98</v>
+      </c>
+      <c r="N100" s="9">
+        <v>100</v>
+      </c>
+      <c r="O100" t="s">
+        <v>183</v>
+      </c>
+      <c r="P100" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
       <c r="N101" s="6"/>
       <c r="Q101" s="6"/>
     </row>
-    <row r="102" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
       <c r="N102" s="6"/>
     </row>
-    <row r="103" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
       <c r="N103" s="6"/>
     </row>
-    <row r="104" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
       <c r="N104" s="6"/>
     </row>
-    <row r="105" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
       <c r="N105" s="6"/>
     </row>
-    <row r="106" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
       <c r="N106" s="6"/>
     </row>
-    <row r="107" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
       <c r="N107" s="6"/>
     </row>
-    <row r="108" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
       <c r="N108" s="6"/>
     </row>
-    <row r="109" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
       <c r="N109" s="6"/>
     </row>
-    <row r="110" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
       <c r="N110" s="6"/>
     </row>
-    <row r="111" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
       <c r="N111" s="6"/>
     </row>
-    <row r="112" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="N112" s="6"/>
     </row>
-    <row r="113" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="113" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
       <c r="N113" s="6"/>
     </row>
-    <row r="114" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="114" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="N114" s="6"/>
     </row>
-    <row r="115" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="115" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
       <c r="N115" s="6"/>
     </row>
-    <row r="116" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="116" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
       <c r="N116" s="6"/>
     </row>
-    <row r="117" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="117" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
       <c r="N117" s="6"/>
     </row>
-    <row r="118" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="118" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C118" s="4"/>
       <c r="D118" s="4"/>
       <c r="N118" s="6"/>
     </row>
-    <row r="119" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="119" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
       <c r="N119" s="6"/>
     </row>
-    <row r="120" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="120" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
       <c r="N120" s="6"/>
     </row>
-    <row r="121" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="121" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C121" s="4"/>
       <c r="D121" s="4"/>
       <c r="N121" s="6"/>
     </row>
-    <row r="122" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="122" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
       <c r="N122" s="6"/>
     </row>
-    <row r="123" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="123" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
       <c r="N123" s="6"/>
     </row>
-    <row r="124" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="124" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C124" s="4"/>
       <c r="D124" s="4"/>
       <c r="N124" s="6"/>
     </row>
-    <row r="125" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="125" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
       <c r="N125" s="6"/>
     </row>
-    <row r="126" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="126" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
       <c r="N126" s="6"/>
     </row>
-    <row r="127" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="127" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
       <c r="N127" s="6"/>
     </row>
-    <row r="128" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="128" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
       <c r="N128" s="6"/>
     </row>
-    <row r="129" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="129" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>
       <c r="N129" s="6"/>
     </row>
-    <row r="130" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="130" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
       <c r="N130" s="6"/>
     </row>
-    <row r="131" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="131" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
       <c r="N131" s="6"/>
     </row>
-    <row r="132" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="132" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
       <c r="N132" s="6"/>
     </row>
-    <row r="133" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="133" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C133" s="4"/>
       <c r="D133" s="4"/>
       <c r="N133" s="6"/>
     </row>
-    <row r="134" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="134" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C134" s="4"/>
       <c r="D134" s="4"/>
       <c r="N134" s="6"/>
     </row>
-    <row r="135" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="135" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C135" s="4"/>
       <c r="D135" s="4"/>
       <c r="N135" s="6"/>
     </row>
-    <row r="136" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="136" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C136" s="4"/>
       <c r="D136" s="4"/>
       <c r="N136" s="6"/>
     </row>
-    <row r="137" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="137" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C137" s="4"/>
       <c r="D137" s="4"/>
       <c r="N137" s="6"/>
     </row>
-    <row r="138" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="138" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C138" s="4"/>
       <c r="D138" s="4"/>
       <c r="N138" s="6"/>
     </row>
-    <row r="139" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="139" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C139" s="4"/>
       <c r="D139" s="4"/>
       <c r="N139" s="6"/>
     </row>
-    <row r="140" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="140" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C140" s="4"/>
       <c r="D140" s="4"/>
       <c r="N140" s="6"/>
     </row>
-    <row r="141" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="141" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C141" s="4"/>
       <c r="D141" s="4"/>
       <c r="N141" s="6"/>
     </row>
-    <row r="142" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="142" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C142" s="4"/>
       <c r="D142" s="4"/>
       <c r="N142" s="6"/>
     </row>
-    <row r="143" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="143" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C143" s="4"/>
       <c r="D143" s="4"/>
       <c r="N143" s="6"/>
     </row>
-    <row r="144" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="144" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C144" s="4"/>
       <c r="D144" s="4"/>
       <c r="N144" s="6"/>
     </row>
-    <row r="145" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="145" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C145" s="4"/>
       <c r="D145" s="4"/>
       <c r="N145" s="6"/>
     </row>
-    <row r="146" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="146" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C146" s="4"/>
       <c r="D146" s="4"/>
       <c r="N146" s="6"/>
     </row>
-    <row r="147" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="147" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C147" s="4"/>
       <c r="D147" s="4"/>
       <c r="N147" s="6"/>
     </row>
-    <row r="148" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="148" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C148" s="4"/>
       <c r="D148" s="4"/>
       <c r="N148" s="6"/>
     </row>
-    <row r="149" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="149" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
       <c r="N149" s="6"/>
     </row>
-    <row r="150" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="150" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C150" s="4"/>
       <c r="D150" s="4"/>
       <c r="N150" s="6"/>
     </row>
-    <row r="151" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="151" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C151" s="4"/>
       <c r="D151" s="4"/>
       <c r="N151" s="6"/>
     </row>
-    <row r="152" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="152" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
       <c r="N152" s="6"/>
     </row>
-    <row r="153" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="153" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C153" s="4"/>
       <c r="D153" s="4"/>
       <c r="N153" s="6"/>
     </row>
-    <row r="154" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="154" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
       <c r="N154" s="6"/>
     </row>
-    <row r="155" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="155" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
       <c r="N155" s="6"/>
     </row>
-    <row r="156" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="156" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
       <c r="N156" s="6"/>
     </row>
-    <row r="157" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="157" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
       <c r="N157" s="6"/>
     </row>
-    <row r="158" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="158" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
       <c r="N158" s="6"/>
     </row>
-    <row r="159" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="159" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="N159" s="6"/>
     </row>
-    <row r="160" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="160" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
       <c r="N160" s="6"/>
     </row>
-    <row r="161" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="161" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
       <c r="N161" s="6"/>
     </row>
-    <row r="162" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="162" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C162" s="4"/>
       <c r="D162" s="4"/>
       <c r="N162" s="6"/>
     </row>
-    <row r="163" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="163" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C163" s="4"/>
       <c r="D163" s="4"/>
       <c r="N163" s="6"/>
     </row>
-    <row r="164" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="164" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C164" s="4"/>
       <c r="D164" s="4"/>
       <c r="N164" s="6"/>
     </row>
-    <row r="165" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="165" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
       <c r="N165" s="6"/>
     </row>
-    <row r="166" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="166" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C166" s="4"/>
       <c r="D166" s="4"/>
       <c r="N166" s="6"/>
     </row>
-    <row r="167" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="167" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C167" s="4"/>
       <c r="D167" s="4"/>
       <c r="N167" s="6"/>
     </row>
-    <row r="168" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="168" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C168" s="4"/>
       <c r="D168" s="4"/>
       <c r="N168" s="6"/>
     </row>
-    <row r="169" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="169" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
       <c r="N169" s="6"/>
     </row>
-    <row r="170" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="170" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C170" s="4"/>
       <c r="D170" s="4"/>
       <c r="N170" s="6"/>
     </row>
-    <row r="171" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="171" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C171" s="4"/>
       <c r="D171" s="4"/>
       <c r="N171" s="6"/>
     </row>
-    <row r="172" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="172" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C172" s="4"/>
       <c r="D172" s="4"/>
       <c r="N172" s="6"/>
     </row>
-    <row r="173" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="173" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C173" s="4"/>
       <c r="D173" s="4"/>
       <c r="N173" s="6"/>
     </row>
-    <row r="174" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="174" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
       <c r="N174" s="6"/>
     </row>
-    <row r="175" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="175" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C175" s="4"/>
       <c r="D175" s="4"/>
       <c r="N175" s="6"/>
     </row>
-    <row r="176" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="176" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C176" s="4"/>
       <c r="D176" s="4"/>
       <c r="N176" s="6"/>
     </row>
-    <row r="177" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="177" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C177" s="4"/>
       <c r="D177" s="4"/>
       <c r="N177" s="6"/>
     </row>
-    <row r="178" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="178" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C178" s="4"/>
       <c r="D178" s="4"/>
       <c r="N178" s="6"/>
     </row>
-    <row r="179" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="179" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C179" s="4"/>
       <c r="D179" s="4"/>
       <c r="N179" s="6"/>
     </row>
-    <row r="180" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="180" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C180" s="4"/>
       <c r="D180" s="4"/>
       <c r="N180" s="6"/>
     </row>
-    <row r="181" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="181" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C181" s="4"/>
       <c r="D181" s="4"/>
       <c r="N181" s="6"/>
     </row>
-    <row r="182" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="182" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C182" s="4"/>
       <c r="D182" s="4"/>
       <c r="N182" s="6"/>
     </row>
-    <row r="183" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="183" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C183" s="4"/>
       <c r="D183" s="4"/>
       <c r="N183" s="6"/>
     </row>
-    <row r="184" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="184" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C184" s="4"/>
       <c r="D184" s="4"/>
       <c r="N184" s="6"/>
     </row>
-    <row r="185" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="185" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C185" s="4"/>
       <c r="D185" s="4"/>
       <c r="N185" s="6"/>
     </row>
-    <row r="186" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="186" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C186" s="4"/>
       <c r="D186" s="4"/>
       <c r="N186" s="6"/>
     </row>
-    <row r="187" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="187" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
       <c r="N187" s="6"/>
     </row>
-    <row r="188" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="188" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C188" s="4"/>
       <c r="D188" s="4"/>
       <c r="N188" s="6"/>
     </row>
-    <row r="189" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="189" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
       <c r="N189" s="6"/>
     </row>
-    <row r="190" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="190" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C190" s="4"/>
       <c r="D190" s="4"/>
       <c r="N190" s="6"/>
     </row>
-    <row r="191" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="191" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C191" s="4"/>
       <c r="D191" s="4"/>
       <c r="N191" s="6"/>
     </row>
-    <row r="192" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="192" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C192" s="4"/>
       <c r="D192" s="4"/>
       <c r="N192" s="6"/>
     </row>
-    <row r="193" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="193" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C193" s="4"/>
       <c r="D193" s="4"/>
       <c r="N193" s="6"/>
     </row>
-    <row r="194" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="194" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C194" s="4"/>
       <c r="D194" s="4"/>
       <c r="N194" s="6"/>
     </row>
-    <row r="195" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="195" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C195" s="4"/>
       <c r="D195" s="4"/>
       <c r="N195" s="6"/>
     </row>
-    <row r="196" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="196" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C196" s="4"/>
       <c r="D196" s="4"/>
       <c r="N196" s="6"/>
     </row>
-    <row r="197" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="197" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C197" s="4"/>
       <c r="D197" s="4"/>
       <c r="N197" s="6"/>
     </row>
-    <row r="198" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="198" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C198" s="4"/>
       <c r="D198" s="4"/>
       <c r="N198" s="6"/>
     </row>
-    <row r="199" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="199" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C199" s="4"/>
       <c r="D199" s="4"/>
       <c r="N199" s="6"/>
     </row>
-    <row r="200" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="200" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C200" s="4"/>
       <c r="D200" s="4"/>
       <c r="N200" s="6"/>
     </row>
-    <row r="201" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="201" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C201" s="4"/>
       <c r="D201" s="4"/>
       <c r="N201" s="6"/>
     </row>
-    <row r="202" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="202" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C202" s="4"/>
       <c r="D202" s="4"/>
     </row>
-    <row r="203" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="203" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C203" s="4"/>
       <c r="D203" s="4"/>
     </row>
-    <row r="204" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="204" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C204" s="4"/>
       <c r="D204" s="4"/>
     </row>
-    <row r="205" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="205" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C205" s="4"/>
       <c r="D205" s="4"/>
     </row>
-    <row r="206" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="206" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C206" s="4"/>
       <c r="D206" s="4"/>
     </row>
-    <row r="207" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="207" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C207" s="4"/>
       <c r="D207" s="4"/>
     </row>
-    <row r="208" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="208" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C208" s="4"/>
       <c r="D208" s="4"/>
     </row>
-    <row r="209" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="209" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C209" s="4"/>
       <c r="D209" s="4"/>
     </row>
-    <row r="210" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="210" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C210" s="4"/>
       <c r="D210" s="4"/>
     </row>
-    <row r="211" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="211" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C211" s="4"/>
       <c r="D211" s="4"/>
     </row>
-    <row r="212" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="212" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C212" s="4"/>
       <c r="D212" s="4"/>
     </row>
-    <row r="213" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="213" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C213" s="4"/>
       <c r="D213" s="4"/>
     </row>
-    <row r="214" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="214" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C214" s="4"/>
       <c r="D214" s="4"/>
     </row>
-    <row r="215" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="215" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C215" s="4"/>
       <c r="D215" s="4"/>
     </row>
-    <row r="216" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="216" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C216" s="4"/>
       <c r="D216" s="4"/>
     </row>
-    <row r="217" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="217" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C217" s="4"/>
       <c r="D217" s="4"/>
     </row>
-    <row r="218" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="218" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C218" s="4"/>
       <c r="D218" s="4"/>
     </row>
-    <row r="219" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="219" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C219" s="4"/>
       <c r="D219" s="4"/>
     </row>
-    <row r="220" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="220" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C220" s="4"/>
       <c r="D220" s="4"/>
     </row>
-    <row r="221" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="221" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C221" s="4"/>
       <c r="D221" s="4"/>
     </row>
-    <row r="222" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="222" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C222" s="4"/>
       <c r="D222" s="4"/>
     </row>
-    <row r="223" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="223" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
     </row>
-    <row r="224" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="224" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
     </row>
-    <row r="225" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="225" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C225" s="4"/>
       <c r="D225" s="4"/>
     </row>
-    <row r="226" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="226" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C226" s="4"/>
       <c r="D226" s="4"/>
     </row>
-    <row r="227" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="227" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C227" s="4"/>
       <c r="D227" s="4"/>
     </row>
-    <row r="228" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="228" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C228" s="4"/>
       <c r="D228" s="4"/>
     </row>
-    <row r="229" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="229" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C229" s="4"/>
       <c r="D229" s="4"/>
     </row>
-    <row r="230" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="230" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C230" s="4"/>
       <c r="D230" s="4"/>
     </row>
-    <row r="231" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="231" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C231" s="4"/>
       <c r="D231" s="4"/>
     </row>
-    <row r="232" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="232" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C232" s="4"/>
       <c r="D232" s="4"/>
     </row>
-    <row r="233" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="233" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C233" s="4"/>
       <c r="D233" s="4"/>
     </row>
-    <row r="234" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="234" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C234" s="4"/>
       <c r="D234" s="4"/>
     </row>
-    <row r="235" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="235" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C235" s="4"/>
       <c r="D235" s="4"/>
     </row>
-    <row r="236" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="236" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C236" s="4"/>
       <c r="D236" s="4"/>
     </row>
-    <row r="237" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="237" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C237" s="4"/>
       <c r="D237" s="4"/>
     </row>
-    <row r="238" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="238" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C238" s="4"/>
       <c r="D238" s="4"/>
     </row>
-    <row r="239" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="239" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C239" s="4"/>
       <c r="D239" s="4"/>
     </row>
-    <row r="240" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="240" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C240" s="4"/>
       <c r="D240" s="4"/>
     </row>
-    <row r="241" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="241" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C241" s="4"/>
       <c r="D241" s="4"/>
     </row>
-    <row r="242" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="242" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C242" s="4"/>
       <c r="D242" s="4"/>
     </row>
-    <row r="243" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="243" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C243" s="4"/>
       <c r="D243" s="4"/>
     </row>
-    <row r="244" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="244" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C244" s="4"/>
       <c r="D244" s="4"/>
     </row>
-    <row r="245" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="245" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C245" s="4"/>
       <c r="D245" s="4"/>
     </row>
-    <row r="246" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="246" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C246" s="4"/>
       <c r="D246" s="4"/>
     </row>
-    <row r="247" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="247" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C247" s="4"/>
       <c r="D247" s="4"/>
     </row>
-    <row r="248" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="248" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C248" s="4"/>
       <c r="D248" s="4"/>
     </row>
-    <row r="249" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="249" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C249" s="4"/>
       <c r="D249" s="4"/>
     </row>
-    <row r="250" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="250" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C250" s="4"/>
       <c r="D250" s="4"/>
     </row>
-    <row r="251" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="251" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C251" s="4"/>
       <c r="D251" s="4"/>
     </row>
-    <row r="252" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="252" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C252" s="4"/>
       <c r="D252" s="4"/>
     </row>
-    <row r="253" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="253" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C253" s="4"/>
       <c r="D253" s="4"/>
     </row>
-    <row r="254" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="254" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C254" s="4"/>
       <c r="D254" s="4"/>
     </row>
-    <row r="255" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="255" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C255" s="4"/>
       <c r="D255" s="4"/>
     </row>
-    <row r="256" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="256" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C256" s="4"/>
       <c r="D256" s="4"/>
     </row>
-    <row r="257" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="257" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C257" s="4"/>
       <c r="D257" s="4"/>
     </row>
-    <row r="258" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="258" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C258" s="4"/>
       <c r="D258" s="4"/>
     </row>
-    <row r="259" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="259" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C259" s="4"/>
       <c r="D259" s="4"/>
     </row>
-    <row r="260" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="260" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C260" s="4"/>
       <c r="D260" s="4"/>
     </row>
-    <row r="261" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="261" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C261" s="4"/>
       <c r="D261" s="4"/>
     </row>
-    <row r="262" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="262" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C262" s="4"/>
       <c r="D262" s="4"/>
     </row>
-    <row r="263" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="263" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C263" s="4"/>
       <c r="D263" s="4"/>
     </row>
-    <row r="264" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="264" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C264" s="4"/>
       <c r="D264" s="4"/>
     </row>
-    <row r="265" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="265" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C265" s="4"/>
       <c r="D265" s="4"/>
     </row>
-    <row r="266" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="266" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C266" s="4"/>
       <c r="D266" s="4"/>
     </row>
-    <row r="267" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="267" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C267" s="4"/>
       <c r="D267" s="4"/>
     </row>
-    <row r="268" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="268" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C268" s="4"/>
       <c r="D268" s="4"/>
     </row>
-    <row r="269" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="269" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C269" s="4"/>
       <c r="D269" s="4"/>
     </row>
-    <row r="270" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="270" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C270" s="4"/>
       <c r="D270" s="4"/>
     </row>
-    <row r="271" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="271" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C271" s="4"/>
       <c r="D271" s="4"/>
     </row>
-    <row r="272" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="272" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C272" s="4"/>
       <c r="D272" s="4"/>
     </row>
-    <row r="273" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="273" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C273" s="4"/>
       <c r="D273" s="4"/>
     </row>
-    <row r="274" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="274" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C274" s="4"/>
       <c r="D274" s="4"/>
     </row>
-    <row r="275" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="275" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C275" s="4"/>
       <c r="D275" s="4"/>
     </row>
-    <row r="276" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="276" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C276" s="4"/>
       <c r="D276" s="4"/>
     </row>
-    <row r="277" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="277" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C277" s="4"/>
       <c r="D277" s="4"/>
     </row>
-    <row r="278" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="278" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C278" s="4"/>
       <c r="D278" s="4"/>
     </row>
-    <row r="279" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="279" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C279" s="4"/>
       <c r="D279" s="4"/>
     </row>
-    <row r="280" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="280" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C280" s="4"/>
       <c r="D280" s="4"/>
     </row>
-    <row r="281" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="281" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C281" s="4"/>
       <c r="D281" s="4"/>
     </row>
-    <row r="282" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="282" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C282" s="4"/>
       <c r="D282" s="4"/>
     </row>
-    <row r="283" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="283" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C283" s="4"/>
       <c r="D283" s="4"/>
     </row>
-    <row r="284" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="284" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C284" s="4"/>
       <c r="D284" s="4"/>
     </row>
-    <row r="285" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="285" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C285" s="4"/>
       <c r="D285" s="4"/>
     </row>
-    <row r="286" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="286" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C286" s="4"/>
       <c r="D286" s="4"/>
     </row>
-    <row r="287" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="287" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C287" s="4"/>
       <c r="D287" s="4"/>
     </row>
-    <row r="288" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="288" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C288" s="4"/>
       <c r="D288" s="4"/>
     </row>
-    <row r="289" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="289" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C289" s="4"/>
       <c r="D289" s="4"/>
     </row>
-    <row r="290" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="290" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C290" s="4"/>
       <c r="D290" s="4"/>
     </row>
-    <row r="291" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="291" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C291" s="4"/>
       <c r="D291" s="4"/>
     </row>
-    <row r="292" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="292" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C292" s="4"/>
       <c r="D292" s="4"/>
     </row>
-    <row r="293" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="293" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C293" s="4"/>
       <c r="D293" s="4"/>
     </row>
-    <row r="294" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="294" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C294" s="4"/>
       <c r="D294" s="4"/>
     </row>
-    <row r="295" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="295" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C295" s="4"/>
       <c r="D295" s="4"/>
     </row>
-    <row r="296" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="296" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C296" s="4"/>
       <c r="D296" s="4"/>
     </row>
-    <row r="297" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="297" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C297" s="4"/>
       <c r="D297" s="4"/>
     </row>
-    <row r="298" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="298" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C298" s="4"/>
       <c r="D298" s="4"/>
     </row>
-    <row r="299" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="299" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C299" s="4"/>
       <c r="D299" s="4"/>
     </row>
-    <row r="300" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="300" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C300" s="4"/>
       <c r="D300" s="4"/>
     </row>
-    <row r="301" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="301" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C301" s="4"/>
       <c r="D301" s="4"/>
     </row>
-    <row r="302" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="302" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C302" s="4"/>
       <c r="D302" s="4"/>
     </row>
-    <row r="303" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="303" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C303" s="4"/>
       <c r="D303" s="4"/>
     </row>
-    <row r="304" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="304" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C304" s="4"/>
       <c r="D304" s="4"/>
     </row>
-    <row r="305" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="305" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C305" s="4"/>
       <c r="D305" s="4"/>
     </row>
-    <row r="306" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="306" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C306" s="4"/>
       <c r="D306" s="4"/>
     </row>
-    <row r="307" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="307" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C307" s="4"/>
       <c r="D307" s="4"/>
     </row>
-    <row r="308" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="308" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C308" s="4"/>
       <c r="D308" s="4"/>
     </row>
-    <row r="309" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="309" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C309" s="4"/>
       <c r="D309" s="4"/>
     </row>
-    <row r="310" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="310" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C310" s="4"/>
       <c r="D310" s="4"/>
     </row>
-    <row r="311" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="311" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C311" s="4"/>
       <c r="D311" s="4"/>
     </row>
-    <row r="312" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="312" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C312" s="4"/>
       <c r="D312" s="4"/>
     </row>
-    <row r="313" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="313" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C313" s="4"/>
       <c r="D313" s="4"/>
     </row>
-    <row r="314" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="314" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C314" s="4"/>
       <c r="D314" s="4"/>
     </row>
-    <row r="315" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="315" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C315" s="4"/>
       <c r="D315" s="4"/>
     </row>
-    <row r="316" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="316" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C316" s="4"/>
       <c r="D316" s="4"/>
     </row>
-    <row r="317" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="317" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C317" s="4"/>
       <c r="D317" s="4"/>
     </row>
-    <row r="318" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="318" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C318" s="4"/>
       <c r="D318" s="4"/>
     </row>
-    <row r="319" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="319" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C319" s="4"/>
       <c r="D319" s="4"/>
     </row>
-    <row r="320" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="320" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C320" s="4"/>
       <c r="D320" s="4"/>
     </row>
-    <row r="321" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="321" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C321" s="4"/>
       <c r="D321" s="4"/>
     </row>
-    <row r="322" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="322" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C322" s="4"/>
       <c r="D322" s="4"/>
     </row>
-    <row r="323" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="323" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C323" s="4"/>
       <c r="D323" s="4"/>
     </row>
-    <row r="324" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="324" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C324" s="4"/>
       <c r="D324" s="4"/>
     </row>
-    <row r="325" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="325" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C325" s="4"/>
       <c r="D325" s="4"/>
     </row>
-    <row r="326" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="326" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C326" s="4"/>
       <c r="D326" s="4"/>
     </row>
-    <row r="327" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="327" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C327" s="4"/>
       <c r="D327" s="4"/>
     </row>
-    <row r="328" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="328" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C328" s="4"/>
       <c r="D328" s="4"/>
     </row>
-    <row r="329" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="329" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C329" s="4"/>
       <c r="D329" s="4"/>
     </row>
-    <row r="330" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="330" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C330" s="4"/>
       <c r="D330" s="4"/>
     </row>
-    <row r="331" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="331" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C331" s="4"/>
       <c r="D331" s="4"/>
     </row>
-    <row r="332" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="332" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C332" s="4"/>
       <c r="D332" s="4"/>
     </row>
-    <row r="333" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="333" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C333" s="4"/>
       <c r="D333" s="4"/>
     </row>
-    <row r="334" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="334" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C334" s="4"/>
       <c r="D334" s="4"/>
     </row>
-    <row r="335" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="335" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C335" s="4"/>
       <c r="D335" s="4"/>
     </row>
-    <row r="336" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="336" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C336" s="4"/>
       <c r="D336" s="4"/>
     </row>
-    <row r="337" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="337" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C337" s="4"/>
       <c r="D337" s="4"/>
     </row>
-    <row r="338" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="338" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C338" s="4"/>
       <c r="D338" s="4"/>
     </row>
-    <row r="339" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="339" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C339" s="4"/>
       <c r="D339" s="4"/>
     </row>
-    <row r="340" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="340" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C340" s="4"/>
       <c r="D340" s="4"/>
     </row>
-    <row r="341" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="341" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C341" s="4"/>
       <c r="D341" s="4"/>
     </row>
-    <row r="342" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="342" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C342" s="4"/>
       <c r="D342" s="4"/>
     </row>
-    <row r="343" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="343" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C343" s="4"/>
       <c r="D343" s="4"/>
     </row>
-    <row r="344" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="344" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C344" s="4"/>
       <c r="D344" s="4"/>
     </row>
-    <row r="345" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="345" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C345" s="4"/>
       <c r="D345" s="4"/>
     </row>
-    <row r="346" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="346" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C346" s="4"/>
       <c r="D346" s="4"/>
     </row>
-    <row r="347" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="347" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C347" s="4"/>
       <c r="D347" s="4"/>
     </row>
-    <row r="348" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="348" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C348" s="4"/>
       <c r="D348" s="4"/>
     </row>
-    <row r="349" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="349" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C349" s="4"/>
       <c r="D349" s="4"/>
     </row>
-    <row r="350" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="350" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C350" s="4"/>
       <c r="D350" s="4"/>
     </row>
-    <row r="351" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="351" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C351" s="4"/>
       <c r="D351" s="4"/>
     </row>
-    <row r="352" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="352" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C352" s="4"/>
       <c r="D352" s="4"/>
     </row>
-    <row r="353" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="353" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C353" s="4"/>
       <c r="D353" s="4"/>
     </row>
-    <row r="354" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="354" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C354" s="4"/>
       <c r="D354" s="4"/>
     </row>
-    <row r="355" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="355" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C355" s="4"/>
       <c r="D355" s="4"/>
     </row>
-    <row r="356" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="356" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C356" s="4"/>
       <c r="D356" s="4"/>
     </row>
-    <row r="357" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="357" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C357" s="4"/>
       <c r="D357" s="4"/>
     </row>
-    <row r="358" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="358" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C358" s="4"/>
       <c r="D358" s="4"/>
     </row>
-    <row r="359" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="359" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C359" s="4"/>
       <c r="D359" s="4"/>
     </row>
-    <row r="360" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="360" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C360" s="4"/>
       <c r="D360" s="4"/>
     </row>
-    <row r="361" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="361" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C361" s="4"/>
       <c r="D361" s="4"/>
     </row>
-    <row r="362" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="362" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C362" s="4"/>
       <c r="D362" s="4"/>
     </row>
-    <row r="363" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="363" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C363" s="4"/>
       <c r="D363" s="4"/>
     </row>
-    <row r="364" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="364" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C364" s="4"/>
       <c r="D364" s="4"/>
     </row>
-    <row r="365" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="365" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C365" s="4"/>
       <c r="D365" s="4"/>
     </row>
-    <row r="366" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="366" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C366" s="4"/>
       <c r="D366" s="4"/>
     </row>
-    <row r="367" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="367" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C367" s="4"/>
       <c r="D367" s="4"/>
     </row>
-    <row r="368" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="368" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C368" s="4"/>
       <c r="D368" s="4"/>
     </row>
-    <row r="369" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="369" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C369" s="4"/>
       <c r="D369" s="4"/>
     </row>
-    <row r="370" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="370" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C370" s="4"/>
       <c r="D370" s="4"/>
     </row>
-    <row r="371" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="371" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C371" s="4"/>
       <c r="D371" s="4"/>
     </row>
-    <row r="372" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="372" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C372" s="4"/>
       <c r="D372" s="4"/>
     </row>
-    <row r="373" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="373" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C373" s="4"/>
       <c r="D373" s="4"/>
     </row>
-    <row r="374" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="374" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C374" s="4"/>
       <c r="D374" s="4"/>
     </row>
-    <row r="375" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="375" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C375" s="4"/>
       <c r="D375" s="4"/>
     </row>
-    <row r="376" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="376" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C376" s="4"/>
       <c r="D376" s="4"/>
     </row>
-    <row r="377" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="377" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C377" s="4"/>
       <c r="D377" s="4"/>
     </row>
-    <row r="378" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="378" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C378" s="4"/>
       <c r="D378" s="4"/>
     </row>
-    <row r="379" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="379" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C379" s="4"/>
       <c r="D379" s="4"/>
     </row>
-    <row r="380" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="380" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C380" s="4"/>
       <c r="D380" s="4"/>
     </row>
-    <row r="381" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="381" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C381" s="4"/>
       <c r="D381" s="4"/>
     </row>
-    <row r="382" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="382" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C382" s="4"/>
       <c r="D382" s="4"/>
     </row>
-    <row r="383" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="383" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C383" s="4"/>
       <c r="D383" s="4"/>
     </row>
-    <row r="384" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="384" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C384" s="4"/>
       <c r="D384" s="4"/>
     </row>
-    <row r="385" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="385" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C385" s="4"/>
       <c r="D385" s="4"/>
     </row>
-    <row r="386" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="386" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C386" s="4"/>
       <c r="D386" s="4"/>
     </row>
-    <row r="387" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="387" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C387" s="4"/>
       <c r="D387" s="4"/>
     </row>
-    <row r="388" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="388" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C388" s="4"/>
       <c r="D388" s="4"/>
     </row>
-    <row r="389" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="389" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C389" s="4"/>
       <c r="D389" s="4"/>
     </row>
-    <row r="390" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="390" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C390" s="4"/>
       <c r="D390" s="4"/>
     </row>
-    <row r="391" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="391" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C391" s="4"/>
       <c r="D391" s="4"/>
     </row>
-    <row r="392" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="392" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C392" s="4"/>
       <c r="D392" s="4"/>
     </row>
-    <row r="393" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="393" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C393" s="4"/>
       <c r="D393" s="4"/>
     </row>
-    <row r="394" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="394" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C394" s="4"/>
       <c r="D394" s="4"/>
     </row>
-    <row r="395" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="395" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C395" s="4"/>
       <c r="D395" s="4"/>
     </row>
-    <row r="396" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="396" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C396" s="4"/>
       <c r="D396" s="4"/>
     </row>
-    <row r="397" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="397" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C397" s="4"/>
       <c r="D397" s="4"/>
     </row>
-    <row r="398" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="398" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C398" s="4"/>
       <c r="D398" s="4"/>
     </row>
-    <row r="399" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="399" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C399" s="4"/>
       <c r="D399" s="4"/>
     </row>
-    <row r="400" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="400" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C400" s="4"/>
       <c r="D400" s="4"/>
     </row>
-    <row r="401" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="401" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C401" s="4"/>
       <c r="D401" s="4"/>
     </row>
-    <row r="402" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="402" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C402" s="4"/>
       <c r="D402" s="4"/>
     </row>
-    <row r="403" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="403" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C403" s="4"/>
       <c r="D403" s="4"/>
     </row>
-    <row r="404" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="404" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C404" s="4"/>
       <c r="D404" s="4"/>
     </row>
-    <row r="405" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="405" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C405" s="4"/>
       <c r="D405" s="4"/>
     </row>
-    <row r="406" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="406" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C406" s="4"/>
       <c r="D406" s="4"/>
     </row>
-    <row r="407" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="407" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C407" s="4"/>
       <c r="D407" s="4"/>
     </row>
-    <row r="408" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="408" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C408" s="4"/>
       <c r="D408" s="4"/>
     </row>
-    <row r="409" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="409" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C409" s="4"/>
       <c r="D409" s="4"/>
     </row>
-    <row r="410" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="410" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C410" s="4"/>
       <c r="D410" s="4"/>
     </row>
-    <row r="411" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="411" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C411" s="4"/>
       <c r="D411" s="4"/>
     </row>
-    <row r="412" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="412" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C412" s="4"/>
       <c r="D412" s="4"/>
     </row>
-    <row r="413" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="413" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C413" s="4"/>
       <c r="D413" s="4"/>
     </row>
-    <row r="414" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="414" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C414" s="4"/>
       <c r="D414" s="4"/>
     </row>
-    <row r="415" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="415" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C415" s="4"/>
       <c r="D415" s="4"/>
       <c r="E415"/>
     </row>
-    <row r="416" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="416" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C416" s="4"/>
       <c r="D416" s="4"/>
       <c r="E416"/>
     </row>
-    <row r="417" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="417" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C417" s="4"/>
       <c r="D417" s="4"/>
       <c r="E417"/>
     </row>
-    <row r="418" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="418" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C418" s="4"/>
       <c r="D418" s="4"/>
       <c r="E418"/>
     </row>
-    <row r="419" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="419" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C419" s="4"/>
       <c r="D419" s="4"/>
       <c r="E419"/>
     </row>
-    <row r="420" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="420" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C420" s="4"/>
       <c r="D420" s="4"/>
       <c r="E420"/>
     </row>
-    <row r="421" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="421" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C421" s="4"/>
       <c r="D421" s="4"/>
       <c r="E421"/>
     </row>
-    <row r="422" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="422" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C422" s="4"/>
       <c r="D422" s="4"/>
       <c r="E422"/>
     </row>
-    <row r="423" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="423" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C423" s="4"/>
       <c r="D423" s="4"/>
       <c r="E423"/>
     </row>
-    <row r="424" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="424" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C424" s="4"/>
       <c r="D424" s="4"/>
       <c r="E424"/>
     </row>
-    <row r="425" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="425" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C425" s="4"/>
       <c r="D425" s="4"/>
       <c r="E425"/>
     </row>
-    <row r="426" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="426" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C426" s="4"/>
       <c r="D426" s="4"/>
       <c r="E426"/>
     </row>
-    <row r="427" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="427" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C427" s="4"/>
       <c r="D427" s="4"/>
       <c r="E427"/>
     </row>
-    <row r="428" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="428" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C428" s="4"/>
       <c r="D428" s="4"/>
       <c r="E428"/>
     </row>
-    <row r="429" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="429" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C429" s="4"/>
       <c r="D429" s="4"/>
       <c r="E429"/>
     </row>
-    <row r="430" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="430" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C430" s="4"/>
       <c r="D430" s="4"/>
       <c r="E430"/>
     </row>
-    <row r="431" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="431" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C431" s="4"/>
       <c r="D431" s="4"/>
       <c r="E431"/>
     </row>
-    <row r="432" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="432" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C432" s="4"/>
       <c r="D432" s="4"/>
       <c r="E432"/>
     </row>
-    <row r="433" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="433" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C433" s="4"/>
       <c r="D433" s="4"/>
       <c r="E433"/>
     </row>
-    <row r="434" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="434" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C434" s="4"/>
       <c r="D434" s="4"/>
       <c r="E434"/>
     </row>
-    <row r="435" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="435" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C435" s="4"/>
       <c r="D435" s="4"/>
       <c r="E435"/>
     </row>
-    <row r="436" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="436" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C436" s="4"/>
       <c r="D436" s="4"/>
       <c r="E436"/>
     </row>
-    <row r="437" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="437" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C437" s="4"/>
       <c r="D437" s="4"/>
       <c r="E437"/>
     </row>
-    <row r="438" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="438" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C438" s="4"/>
       <c r="D438" s="4"/>
       <c r="E438"/>
     </row>
-    <row r="439" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="439" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C439" s="4"/>
       <c r="D439" s="4"/>
       <c r="E439"/>
     </row>
-    <row r="440" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="440" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C440" s="4"/>
       <c r="D440" s="4"/>
       <c r="E440"/>
     </row>
-    <row r="441" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="441" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C441" s="4"/>
       <c r="D441" s="4"/>
       <c r="E441"/>
     </row>
-    <row r="442" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="442" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C442" s="4"/>
       <c r="D442" s="4"/>
       <c r="E442"/>
     </row>
-    <row r="443" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="443" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C443" s="4"/>
       <c r="D443" s="4"/>
       <c r="E443"/>
     </row>
-    <row r="444" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="444" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C444" s="4"/>
       <c r="D444" s="4"/>
       <c r="E444"/>
     </row>
-    <row r="445" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="445" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C445" s="4"/>
       <c r="D445" s="4"/>
       <c r="E445"/>
     </row>
-    <row r="446" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="446" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C446" s="4"/>
       <c r="D446" s="4"/>
       <c r="E446"/>
     </row>
-    <row r="447" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="447" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C447" s="4"/>
       <c r="D447" s="4"/>
       <c r="E447"/>
     </row>
-    <row r="448" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="448" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C448" s="4"/>
       <c r="D448" s="4"/>
       <c r="E448"/>
     </row>
-    <row r="449" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="449" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C449" s="4"/>
       <c r="D449" s="4"/>
       <c r="E449"/>
     </row>
-    <row r="450" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="450" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C450" s="4"/>
       <c r="D450" s="4"/>
       <c r="E450"/>
     </row>
-    <row r="451" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="451" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C451" s="4"/>
       <c r="D451" s="4"/>
       <c r="E451"/>
     </row>
-    <row r="452" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="452" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C452" s="4"/>
       <c r="D452" s="4"/>
       <c r="E452"/>
     </row>
-    <row r="453" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="453" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C453" s="4"/>
       <c r="D453" s="4"/>
       <c r="E453"/>
     </row>
-    <row r="454" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="454" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C454" s="4"/>
       <c r="D454" s="4"/>
       <c r="E454"/>
     </row>
-    <row r="455" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="455" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C455" s="4"/>
       <c r="D455" s="4"/>
       <c r="E455"/>
     </row>
-    <row r="456" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="456" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C456" s="4"/>
       <c r="D456" s="4"/>
       <c r="E456"/>
     </row>
-    <row r="457" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="457" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C457" s="4"/>
       <c r="D457" s="4"/>
       <c r="E457"/>
     </row>
-    <row r="458" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="458" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C458" s="4"/>
       <c r="D458" s="4"/>
       <c r="E458"/>
     </row>
-    <row r="459" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="459" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C459" s="4"/>
       <c r="D459" s="4"/>
       <c r="E459"/>
     </row>
-    <row r="460" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="460" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C460" s="4"/>
       <c r="D460" s="4"/>
       <c r="E460"/>
     </row>
-    <row r="461" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="461" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C461" s="4"/>
       <c r="D461" s="4"/>
       <c r="E461"/>
     </row>
-    <row r="462" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="462" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C462" s="4"/>
       <c r="D462" s="4"/>
       <c r="E462"/>
     </row>
-    <row r="463" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="463" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C463" s="4"/>
       <c r="D463" s="4"/>
       <c r="E463"/>
     </row>
-    <row r="464" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="464" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C464" s="4"/>
       <c r="D464" s="4"/>
       <c r="E464"/>
     </row>
-    <row r="465" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="465" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C465" s="4"/>
       <c r="D465" s="4"/>
       <c r="E465"/>
     </row>
-    <row r="466" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="466" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C466" s="4"/>
       <c r="D466" s="4"/>
       <c r="E466"/>
     </row>
-    <row r="467" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="467" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C467" s="4"/>
       <c r="D467" s="4"/>
       <c r="E467"/>
     </row>
-    <row r="468" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="468" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C468" s="4"/>
       <c r="D468" s="4"/>
       <c r="E468"/>
     </row>
-    <row r="469" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="469" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C469" s="4"/>
       <c r="D469" s="4"/>
       <c r="E469"/>
     </row>
-    <row r="470" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="470" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C470" s="4"/>
       <c r="D470" s="4"/>
       <c r="E470"/>
     </row>
-    <row r="471" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="471" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C471" s="4"/>
       <c r="D471" s="4"/>
       <c r="E471"/>
     </row>
-    <row r="472" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="472" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C472" s="4"/>
       <c r="D472" s="4"/>
       <c r="E472"/>
     </row>
-    <row r="473" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="473" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C473" s="4"/>
       <c r="D473" s="4"/>
       <c r="E473"/>
     </row>
-    <row r="474" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="474" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C474" s="4"/>
       <c r="D474" s="4"/>
       <c r="E474"/>
     </row>
-    <row r="475" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="475" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C475" s="4"/>
       <c r="D475" s="4"/>
       <c r="E475"/>
     </row>
-    <row r="476" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="476" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C476" s="4"/>
       <c r="D476" s="4"/>
       <c r="E476"/>
     </row>
-    <row r="477" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="477" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C477" s="4"/>
       <c r="D477" s="4"/>
       <c r="E477"/>
     </row>
-    <row r="478" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="478" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C478" s="4"/>
       <c r="D478" s="4"/>
       <c r="E478"/>
     </row>
-    <row r="479" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="479" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C479" s="4"/>
       <c r="D479" s="4"/>
       <c r="E479"/>
     </row>
-    <row r="480" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="480" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C480" s="4"/>
       <c r="D480" s="4"/>
       <c r="E480"/>
     </row>
-    <row r="481" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="481" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C481" s="4"/>
       <c r="D481" s="4"/>
       <c r="E481"/>
     </row>
-    <row r="482" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="482" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C482" s="4"/>
       <c r="D482" s="4"/>
       <c r="E482"/>
     </row>
-    <row r="483" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="483" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C483" s="4"/>
       <c r="D483" s="4"/>
       <c r="E483"/>
     </row>
-    <row r="484" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="484" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C484" s="4"/>
       <c r="D484" s="4"/>
       <c r="E484"/>
     </row>
-    <row r="485" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="485" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C485" s="4"/>
       <c r="D485" s="4"/>
       <c r="E485"/>
     </row>
-    <row r="486" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="486" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C486" s="4"/>
       <c r="D486" s="4"/>
       <c r="E486"/>
     </row>
-    <row r="487" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="487" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C487" s="4"/>
       <c r="D487" s="4"/>
       <c r="E487"/>
     </row>
-    <row r="488" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="488" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C488" s="4"/>
       <c r="D488" s="4"/>
       <c r="E488"/>
     </row>
-    <row r="489" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="489" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C489" s="4"/>
       <c r="D489" s="4"/>
       <c r="E489"/>
     </row>
-    <row r="490" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="490" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C490" s="4"/>
       <c r="D490" s="4"/>
       <c r="E490"/>
     </row>
-    <row r="491" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="491" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C491" s="4"/>
       <c r="D491" s="4"/>
       <c r="E491"/>
     </row>
-    <row r="492" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="492" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C492" s="4"/>
       <c r="D492" s="4"/>
       <c r="E492"/>
     </row>
-    <row r="493" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="493" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C493" s="4"/>
       <c r="D493" s="4"/>
       <c r="E493"/>
     </row>
-    <row r="494" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="494" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C494" s="4"/>
       <c r="D494" s="4"/>
       <c r="E494"/>
     </row>
-    <row r="495" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="495" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C495" s="4"/>
       <c r="D495" s="4"/>
     </row>
-    <row r="496" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="496" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C496" s="4"/>
       <c r="D496" s="4"/>
     </row>
-    <row r="497" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="497" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C497" s="4"/>
       <c r="D497" s="4"/>
     </row>
-    <row r="498" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="498" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C498" s="4"/>
       <c r="D498" s="4"/>
     </row>
-    <row r="499" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="499" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C499" s="4"/>
       <c r="D499" s="4"/>
     </row>
-    <row r="500" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="500" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C500" s="4"/>
       <c r="D500" s="4"/>
     </row>
-    <row r="501" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="501" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C501" s="4"/>
       <c r="D501" s="4"/>
     </row>
-    <row r="502" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="502" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C502" s="4"/>
       <c r="D502" s="4"/>
     </row>
-    <row r="503" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="503" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C503" s="4"/>
       <c r="D503" s="4"/>
     </row>
-    <row r="504" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="504" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C504" s="4"/>
       <c r="D504" s="4"/>
     </row>
-    <row r="505" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="505" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C505" s="4"/>
       <c r="D505" s="4"/>
     </row>
-    <row r="506" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="506" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C506" s="4"/>
       <c r="D506" s="4"/>
     </row>
-    <row r="507" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="507" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C507" s="4"/>
       <c r="D507" s="4"/>
     </row>
-    <row r="508" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="508" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C508" s="4"/>
       <c r="D508" s="4"/>
     </row>
-    <row r="509" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="509" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C509" s="4"/>
       <c r="D509" s="4"/>
     </row>
-    <row r="510" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="510" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C510" s="4"/>
       <c r="D510" s="4"/>
     </row>
-    <row r="511" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="511" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C511" s="4"/>
       <c r="D511" s="4"/>
     </row>
-    <row r="512" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="512" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C512" s="4"/>
       <c r="D512" s="4"/>
     </row>
-    <row r="513" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="513" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C513" s="4"/>
       <c r="D513" s="4"/>
     </row>
-    <row r="514" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="514" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C514" s="4"/>
       <c r="D514" s="4"/>
     </row>
-    <row r="515" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="515" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C515" s="4"/>
       <c r="D515" s="4"/>
     </row>
-    <row r="516" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="516" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C516" s="4"/>
       <c r="D516" s="4"/>
     </row>
-    <row r="517" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="517" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C517" s="4"/>
       <c r="D517" s="4"/>
     </row>
-    <row r="518" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="518" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C518" s="4"/>
       <c r="D518" s="4"/>
     </row>
-    <row r="519" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="519" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C519" s="4"/>
       <c r="D519" s="4"/>
     </row>
-    <row r="520" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="520" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C520" s="4"/>
       <c r="D520" s="4"/>
     </row>
-    <row r="521" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="521" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C521" s="4"/>
       <c r="D521" s="4"/>
     </row>
-    <row r="522" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="522" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C522" s="4"/>
       <c r="D522" s="4"/>
     </row>
-    <row r="523" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="523" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C523" s="4"/>
       <c r="D523" s="4"/>
     </row>
-    <row r="524" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="524" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C524" s="4"/>
       <c r="D524" s="4"/>
     </row>
-    <row r="525" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="525" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C525" s="4"/>
       <c r="D525" s="4"/>
     </row>
-    <row r="526" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="526" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C526" s="4"/>
       <c r="D526" s="4"/>
     </row>
-    <row r="527" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="527" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C527" s="4"/>
       <c r="D527" s="4"/>
     </row>
-    <row r="528" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="528" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C528" s="4"/>
       <c r="D528" s="4"/>
     </row>
-    <row r="529" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="529" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C529" s="4"/>
       <c r="D529" s="4"/>
     </row>
-    <row r="530" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="530" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C530" s="4"/>
       <c r="D530" s="4"/>
     </row>
-    <row r="531" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="531" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C531" s="4"/>
       <c r="D531" s="4"/>
     </row>
-    <row r="532" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="532" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C532" s="4"/>
       <c r="D532" s="4"/>
     </row>
-    <row r="533" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="533" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C533" s="4"/>
       <c r="D533" s="4"/>
     </row>
-    <row r="534" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="534" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C534" s="4"/>
       <c r="D534" s="4"/>
     </row>
-    <row r="535" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="535" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C535" s="4"/>
       <c r="D535" s="4"/>
     </row>
-    <row r="536" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="536" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C536" s="4"/>
       <c r="D536" s="4"/>
     </row>
-    <row r="537" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="537" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C537" s="4"/>
       <c r="D537" s="4"/>
     </row>
-    <row r="538" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="538" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C538" s="4"/>
       <c r="D538" s="4"/>
     </row>
-    <row r="539" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="539" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C539" s="4"/>
       <c r="D539" s="4"/>
     </row>
-    <row r="540" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="540" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C540" s="4"/>
       <c r="D540" s="4"/>
     </row>
-    <row r="541" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="541" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C541" s="4"/>
       <c r="D541" s="4"/>
     </row>
-    <row r="542" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="542" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C542" s="4"/>
       <c r="D542" s="4"/>
     </row>
-    <row r="543" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="543" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C543" s="4"/>
       <c r="D543" s="4"/>
     </row>
-    <row r="544" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="544" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C544" s="4"/>
       <c r="D544" s="4"/>
     </row>
-    <row r="545" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="545" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C545" s="4"/>
       <c r="D545" s="4"/>
     </row>
-    <row r="546" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="546" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C546" s="4"/>
       <c r="D546" s="4"/>
     </row>
-    <row r="547" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="547" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C547" s="4"/>
       <c r="D547" s="4"/>
     </row>
-    <row r="548" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="548" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C548" s="4"/>
       <c r="D548" s="4"/>
     </row>
-    <row r="549" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="549" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C549" s="4"/>
       <c r="D549" s="4"/>
     </row>
-    <row r="550" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="550" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C550" s="4"/>
       <c r="D550" s="4"/>
     </row>
-    <row r="551" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="551" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C551" s="4"/>
       <c r="D551" s="4"/>
     </row>
-    <row r="552" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="552" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C552" s="4"/>
       <c r="D552" s="4"/>
     </row>
-    <row r="553" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="553" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C553" s="4"/>
       <c r="D553" s="4"/>
     </row>
-    <row r="554" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="554" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C554" s="4"/>
       <c r="D554" s="4"/>
     </row>
-    <row r="555" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="555" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C555" s="4"/>
       <c r="D555" s="4"/>
     </row>
-    <row r="556" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="556" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C556" s="4"/>
       <c r="D556" s="4"/>
     </row>
-    <row r="557" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="557" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C557" s="4"/>
       <c r="D557" s="4"/>
     </row>
-    <row r="558" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="558" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C558" s="4"/>
       <c r="D558" s="4"/>
     </row>
-    <row r="559" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="559" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C559" s="4"/>
       <c r="D559" s="4"/>
     </row>
-    <row r="560" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="560" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C560" s="4"/>
       <c r="D560" s="4"/>
     </row>
-    <row r="561" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="561" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C561" s="4"/>
       <c r="D561" s="4"/>
     </row>
-    <row r="562" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="562" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C562" s="4"/>
       <c r="D562" s="4"/>
     </row>
-    <row r="563" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="563" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C563" s="4"/>
       <c r="D563" s="4"/>
     </row>
-    <row r="564" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="564" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C564" s="4"/>
       <c r="D564" s="4"/>
     </row>
-    <row r="565" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="565" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C565" s="4"/>
       <c r="D565" s="4"/>
     </row>
-    <row r="566" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="566" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C566" s="4"/>
       <c r="D566" s="4"/>
     </row>
-    <row r="567" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="567" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C567" s="4"/>
       <c r="D567" s="4"/>
     </row>
-    <row r="568" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="568" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C568" s="4"/>
       <c r="D568" s="4"/>
     </row>
-    <row r="569" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="569" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C569" s="4"/>
       <c r="D569" s="4"/>
     </row>
-    <row r="570" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="570" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C570" s="4"/>
       <c r="D570" s="4"/>
     </row>
-    <row r="571" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="571" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C571" s="4"/>
       <c r="D571" s="4"/>
     </row>
-    <row r="572" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="572" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C572" s="4"/>
       <c r="D572" s="4"/>
     </row>
-    <row r="573" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="573" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C573" s="4"/>
       <c r="D573" s="4"/>
     </row>
-    <row r="574" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="574" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C574" s="4"/>
       <c r="D574" s="4"/>
     </row>
-    <row r="575" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="575" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C575" s="4"/>
       <c r="D575" s="4"/>
     </row>
-    <row r="576" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="576" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C576" s="4"/>
       <c r="D576" s="4"/>
     </row>
-    <row r="577" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="577" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C577" s="4"/>
       <c r="D577" s="4"/>
     </row>
-    <row r="578" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="578" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C578" s="4"/>
       <c r="D578" s="4"/>
     </row>
-    <row r="579" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="579" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C579" s="4"/>
       <c r="D579" s="4"/>
     </row>
-    <row r="580" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="580" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C580" s="4"/>
       <c r="D580" s="4"/>
     </row>
-    <row r="581" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="581" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C581" s="4"/>
       <c r="D581" s="4"/>
     </row>
-    <row r="582" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="582" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C582" s="4"/>
       <c r="D582" s="4"/>
     </row>
-    <row r="583" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="583" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C583" s="4"/>
       <c r="D583" s="4"/>
     </row>
-    <row r="584" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="584" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C584" s="4"/>
       <c r="D584" s="4"/>
     </row>
-    <row r="585" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="585" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C585" s="4"/>
       <c r="D585" s="4"/>
     </row>
-    <row r="586" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="586" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C586" s="4"/>
       <c r="D586" s="4"/>
     </row>
-    <row r="587" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="587" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C587" s="4"/>
       <c r="D587" s="4"/>
     </row>
-    <row r="588" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="588" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C588" s="4"/>
       <c r="D588" s="4"/>
     </row>
-    <row r="589" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="589" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C589" s="4"/>
       <c r="D589" s="4"/>
     </row>
-    <row r="590" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="590" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C590" s="4"/>
       <c r="D590" s="4"/>
     </row>
-    <row r="591" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="591" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C591" s="4"/>
       <c r="D591" s="4"/>
     </row>
-    <row r="592" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="592" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C592" s="4"/>
       <c r="D592" s="4"/>
     </row>
-    <row r="593" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="593" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C593" s="4"/>
       <c r="D593" s="4"/>
     </row>
-    <row r="594" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="594" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C594" s="4"/>
       <c r="D594" s="4"/>
     </row>
-    <row r="595" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="595" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C595" s="4"/>
       <c r="D595" s="4"/>
     </row>
-    <row r="596" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="596" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C596" s="4"/>
       <c r="D596" s="4"/>
     </row>
-    <row r="597" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="597" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C597" s="4"/>
       <c r="D597" s="4"/>
     </row>
-    <row r="598" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="598" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C598" s="4"/>
       <c r="D598" s="4"/>
     </row>
-    <row r="599" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="599" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C599" s="4"/>
       <c r="D599" s="4"/>
     </row>
-    <row r="600" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="600" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C600" s="4"/>
       <c r="D600" s="4"/>
     </row>
-    <row r="601" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="601" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C601" s="4"/>
       <c r="D601" s="4"/>
     </row>
-    <row r="602" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="602" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C602" s="4"/>
       <c r="D602" s="4"/>
     </row>
-    <row r="603" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="603" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C603" s="4"/>
       <c r="D603" s="4"/>
     </row>
-    <row r="604" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="604" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C604" s="4"/>
       <c r="D604" s="4"/>
     </row>
-    <row r="605" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="605" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C605" s="4"/>
       <c r="D605" s="4"/>
     </row>
-    <row r="606" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="606" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C606" s="4"/>
       <c r="D606" s="4"/>
       <c r="N606" s="13"/>
     </row>
-    <row r="607" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="607" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C607" s="4"/>
       <c r="D607" s="4"/>
       <c r="N607" s="13"/>
     </row>
-    <row r="608" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="608" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C608" s="4"/>
       <c r="D608" s="4"/>
       <c r="N608" s="13"/>
     </row>
-    <row r="609" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="609" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C609" s="4"/>
       <c r="D609" s="4"/>
     </row>
-    <row r="610" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="610" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C610" s="14"/>
       <c r="D610" s="4"/>
     </row>
-    <row r="611" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="611" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C611" s="14"/>
       <c r="D611" s="4"/>
     </row>
-    <row r="612" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="612" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C612" s="14"/>
       <c r="D612" s="4"/>
     </row>
-    <row r="613" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="613" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C613" s="14"/>
       <c r="D613" s="4"/>
     </row>
-    <row r="614" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="614" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C614" s="14"/>
       <c r="D614" s="4"/>
     </row>
-    <row r="615" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="615" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C615" s="14"/>
       <c r="D615" s="4"/>
     </row>
-    <row r="616" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="616" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C616" s="14"/>
       <c r="D616" s="4"/>
     </row>
-    <row r="617" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="617" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C617" s="14"/>
       <c r="D617" s="4"/>
     </row>
-    <row r="618" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="618" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C618" s="14"/>
       <c r="D618" s="4"/>
     </row>
-    <row r="619" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="619" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C619" s="14"/>
       <c r="D619" s="4"/>
     </row>
-    <row r="620" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="620" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C620" s="14"/>
       <c r="D620" s="4"/>
     </row>
-    <row r="621" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="621" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C621" s="14"/>
       <c r="D621" s="4"/>
     </row>
-    <row r="622" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="622" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C622" s="14"/>
       <c r="D622" s="4"/>
     </row>
-    <row r="623" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="623" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C623" s="14"/>
       <c r="D623" s="4"/>
     </row>
-    <row r="624" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="624" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C624" s="14"/>
       <c r="D624" s="4"/>
     </row>
-    <row r="625" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="625" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C625" s="14"/>
       <c r="D625" s="4"/>
     </row>
-    <row r="626" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="626" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C626" s="14"/>
       <c r="D626" s="4"/>
     </row>
-    <row r="627" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="627" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C627" s="14"/>
       <c r="D627" s="4"/>
     </row>
-    <row r="628" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="628" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C628" s="14"/>
       <c r="D628" s="4"/>
     </row>
-    <row r="629" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="629" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C629" s="14"/>
       <c r="D629" s="4"/>
     </row>
-    <row r="630" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="630" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C630" s="14"/>
       <c r="D630" s="4"/>
     </row>
-    <row r="631" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="631" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C631" s="14"/>
       <c r="D631" s="4"/>
     </row>
-    <row r="632" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="632" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C632" s="14"/>
       <c r="D632" s="4"/>
     </row>
-    <row r="633" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="633" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C633" s="14"/>
       <c r="D633" s="4"/>
     </row>
-    <row r="634" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="634" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C634" s="14"/>
       <c r="D634" s="4"/>
     </row>
-    <row r="635" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="635" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C635" s="14"/>
       <c r="D635" s="4"/>
     </row>
-    <row r="636" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="636" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C636" s="14"/>
       <c r="D636" s="4"/>
     </row>
-    <row r="637" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="637" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C637" s="14"/>
       <c r="D637" s="4"/>
     </row>
-    <row r="638" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="638" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C638" s="14"/>
       <c r="D638" s="4"/>
       <c r="E638"/>
     </row>
-    <row r="639" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="639" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C639" s="14"/>
       <c r="D639" s="4"/>
       <c r="E639"/>
     </row>
-    <row r="640" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="640" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C640" s="14"/>
       <c r="D640" s="4"/>
       <c r="E640"/>
     </row>
-    <row r="641" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="641" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C641" s="14"/>
       <c r="D641" s="4"/>
       <c r="E641"/>
     </row>
-    <row r="642" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="642" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C642" s="14"/>
       <c r="D642" s="4"/>
       <c r="E642"/>
     </row>
-    <row r="643" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="643" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C643" s="14"/>
       <c r="D643" s="4"/>
       <c r="E643"/>
     </row>
-    <row r="644" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="644" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C644" s="14"/>
       <c r="D644" s="4"/>
       <c r="E644"/>
     </row>
-    <row r="645" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="645" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C645" s="14"/>
       <c r="D645" s="4"/>
       <c r="E645"/>
     </row>
-    <row r="646" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="646" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C646" s="14"/>
       <c r="D646" s="4"/>
       <c r="E646"/>
     </row>
-    <row r="647" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="647" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C647" s="14"/>
       <c r="D647" s="4"/>
       <c r="E647"/>
     </row>
-    <row r="648" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="648" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C648" s="14"/>
       <c r="D648" s="4"/>
       <c r="E648"/>
     </row>
-    <row r="649" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="649" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C649" s="14"/>
       <c r="D649" s="4"/>
       <c r="E649"/>
     </row>
-    <row r="650" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="650" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C650" s="14"/>
       <c r="D650" s="4"/>
       <c r="E650"/>
     </row>
-    <row r="651" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="651" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C651" s="14"/>
       <c r="D651" s="4"/>
       <c r="E651"/>
     </row>
-    <row r="652" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="652" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C652" s="14"/>
       <c r="D652" s="4"/>
       <c r="E652"/>
     </row>
-    <row r="653" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="653" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C653" s="14"/>
       <c r="D653" s="4"/>
       <c r="E653"/>
     </row>
-    <row r="654" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="654" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C654" s="14"/>
       <c r="D654" s="4"/>
       <c r="E654"/>
     </row>
-    <row r="655" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="655" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C655" s="14"/>
       <c r="D655" s="4"/>
       <c r="E655"/>
     </row>
-    <row r="656" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="656" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C656" s="14"/>
       <c r="D656" s="4"/>
       <c r="E656"/>
     </row>
-    <row r="657" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="657" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C657" s="14"/>
       <c r="D657" s="4"/>
       <c r="E657"/>
     </row>
-    <row r="658" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="658" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C658" s="14"/>
       <c r="D658" s="4"/>
       <c r="E658"/>
     </row>
-    <row r="659" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="659" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C659" s="14"/>
       <c r="D659" s="4"/>
       <c r="E659"/>
     </row>
-    <row r="660" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="660" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C660" s="14"/>
       <c r="D660" s="4"/>
       <c r="E660"/>
     </row>
-    <row r="661" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="661" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C661" s="14"/>
       <c r="D661" s="4"/>
       <c r="E661"/>
     </row>
-    <row r="662" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="662" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C662" s="14"/>
       <c r="D662" s="4"/>
       <c r="E662"/>
     </row>
-    <row r="663" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="663" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C663" s="14"/>
       <c r="D663" s="4"/>
       <c r="E663"/>
     </row>
-    <row r="664" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="664" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C664" s="14"/>
       <c r="D664" s="4"/>
       <c r="E664"/>
     </row>
-    <row r="665" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="665" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C665" s="14"/>
       <c r="D665" s="4"/>
       <c r="E665"/>
     </row>
-    <row r="666" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="666" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C666" s="14"/>
       <c r="D666" s="4"/>
       <c r="E666"/>
     </row>
-    <row r="667" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="667" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C667" s="14"/>
       <c r="D667" s="4"/>
       <c r="E667"/>
     </row>
-    <row r="668" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="668" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C668" s="14"/>
       <c r="D668" s="4"/>
       <c r="E668"/>
       <c r="L668" s="7"/>
     </row>
-    <row r="669" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="669" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C669" s="14"/>
       <c r="D669" s="4"/>
       <c r="E669"/>
       <c r="L669" s="7"/>
     </row>
-    <row r="670" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="670" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C670" s="14"/>
       <c r="D670" s="4"/>
       <c r="E670"/>
       <c r="L670" s="7"/>
     </row>
-    <row r="671" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="671" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C671" s="14"/>
       <c r="D671" s="4"/>
       <c r="E671"/>
       <c r="L671" s="7"/>
     </row>
-    <row r="672" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="672" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C672" s="14"/>
       <c r="D672" s="4"/>
       <c r="E672"/>
       <c r="L672" s="7"/>
     </row>
-    <row r="673" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="673" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C673" s="14"/>
       <c r="D673" s="4"/>
       <c r="E673"/>
       <c r="L673" s="7"/>
     </row>
-    <row r="674" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="674" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C674" s="14"/>
       <c r="D674" s="4"/>
       <c r="E674"/>
       <c r="L674" s="7"/>
     </row>
-    <row r="675" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="675" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C675" s="14"/>
       <c r="D675" s="4"/>
       <c r="E675"/>
       <c r="L675" s="7"/>
     </row>
-    <row r="676" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="676" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C676" s="14"/>
       <c r="D676" s="4"/>
       <c r="E676"/>
       <c r="L676" s="7"/>
     </row>
-    <row r="677" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="677" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C677" s="14"/>
       <c r="D677" s="4"/>
       <c r="E677"/>
       <c r="L677" s="7"/>
     </row>
-    <row r="678" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="678" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C678" s="14"/>
       <c r="D678" s="4"/>
       <c r="E678"/>
       <c r="L678" s="7"/>
     </row>
-    <row r="679" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="679" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C679" s="14"/>
       <c r="D679" s="4"/>
       <c r="E679"/>
       <c r="L679" s="7"/>
     </row>
-    <row r="680" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="680" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C680" s="14"/>
       <c r="D680" s="4"/>
       <c r="E680"/>
       <c r="L680" s="7"/>
     </row>
-    <row r="681" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="681" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C681" s="14"/>
       <c r="D681" s="4"/>
       <c r="E681"/>
       <c r="L681" s="7"/>
     </row>
-    <row r="682" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="682" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C682" s="14"/>
       <c r="D682" s="4"/>
       <c r="E682"/>
       <c r="L682" s="7"/>
     </row>
-    <row r="683" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="683" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C683" s="14"/>
       <c r="D683" s="4"/>
       <c r="E683"/>
       <c r="L683" s="7"/>
     </row>
-    <row r="684" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="684" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C684" s="14"/>
       <c r="D684" s="4"/>
       <c r="E684"/>
       <c r="L684" s="7"/>
     </row>
-    <row r="685" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="685" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C685" s="14"/>
       <c r="D685" s="4"/>
       <c r="E685"/>
       <c r="L685" s="7"/>
     </row>
-    <row r="686" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="686" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C686" s="14"/>
       <c r="D686" s="4"/>
       <c r="E686"/>
       <c r="L686" s="7"/>
     </row>
-    <row r="687" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="687" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C687" s="14"/>
       <c r="D687" s="4"/>
       <c r="E687"/>
       <c r="L687" s="7"/>
     </row>
-    <row r="688" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="688" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C688" s="14"/>
       <c r="D688" s="4"/>
       <c r="E688"/>
       <c r="L688" s="7"/>
     </row>
-    <row r="689" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="689" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C689" s="14"/>
       <c r="D689" s="4"/>
       <c r="E689"/>
       <c r="L689" s="7"/>
     </row>
-    <row r="690" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="690" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C690" s="14"/>
       <c r="D690" s="4"/>
       <c r="E690"/>
       <c r="L690" s="7"/>
     </row>
-    <row r="691" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="691" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C691" s="14"/>
       <c r="D691" s="4"/>
       <c r="E691"/>
       <c r="L691" s="7"/>
     </row>
-    <row r="692" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="692" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C692" s="14"/>
       <c r="D692" s="4"/>
       <c r="E692"/>
       <c r="L692" s="7"/>
     </row>
-    <row r="693" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="693" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C693" s="14"/>
       <c r="D693" s="4"/>
       <c r="E693"/>
       <c r="L693" s="7"/>
     </row>
-    <row r="694" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="694" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C694" s="14"/>
       <c r="D694" s="4"/>
       <c r="E694"/>
       <c r="L694" s="7"/>
     </row>
-    <row r="695" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="695" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C695" s="14"/>
       <c r="D695" s="4"/>
       <c r="E695"/>
       <c r="L695" s="7"/>
     </row>
-    <row r="696" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="696" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C696" s="14"/>
       <c r="D696" s="4"/>
       <c r="E696"/>
       <c r="L696" s="7"/>
     </row>
-    <row r="697" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="697" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C697" s="14"/>
       <c r="D697" s="4"/>
       <c r="E697"/>
       <c r="L697" s="7"/>
     </row>
-    <row r="698" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="698" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C698" s="14"/>
       <c r="D698" s="4"/>
       <c r="E698"/>
       <c r="L698" s="7"/>
     </row>
-    <row r="699" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="699" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C699" s="14"/>
       <c r="D699" s="4"/>
       <c r="E699"/>
       <c r="L699" s="7"/>
     </row>
-    <row r="700" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="700" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C700" s="14"/>
       <c r="D700" s="4"/>
       <c r="E700"/>
       <c r="L700" s="7"/>
     </row>
-    <row r="701" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="701" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C701" s="14"/>
       <c r="D701" s="4"/>
       <c r="E701"/>
       <c r="L701" s="7"/>
     </row>
-    <row r="702" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="702" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C702" s="14"/>
       <c r="D702" s="4"/>
       <c r="E702"/>
       <c r="L702" s="7"/>
     </row>
-    <row r="703" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="703" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C703" s="14"/>
       <c r="D703" s="4"/>
       <c r="E703"/>
       <c r="L703" s="7"/>
     </row>
-    <row r="704" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="704" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C704" s="14"/>
       <c r="D704" s="4"/>
       <c r="E704"/>
       <c r="L704" s="7"/>
     </row>
-    <row r="705" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="705" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C705" s="14"/>
       <c r="D705" s="4"/>
       <c r="E705"/>
       <c r="L705" s="7"/>
     </row>
-    <row r="706" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="706" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C706" s="14"/>
       <c r="D706" s="4"/>
       <c r="E706"/>
       <c r="L706" s="7"/>
     </row>
-    <row r="707" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="707" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C707" s="14"/>
       <c r="D707" s="4"/>
       <c r="E707"/>
       <c r="L707" s="7"/>
     </row>
-    <row r="708" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="708" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C708" s="14"/>
       <c r="D708" s="4"/>
       <c r="E708"/>
       <c r="L708" s="7"/>
     </row>
-    <row r="709" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="709" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C709" s="14"/>
       <c r="D709" s="4"/>
       <c r="E709"/>
       <c r="L709" s="7"/>
     </row>
-    <row r="710" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="710" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C710" s="14"/>
       <c r="D710" s="4"/>
       <c r="E710"/>
       <c r="L710" s="7"/>
     </row>
-    <row r="711" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="711" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C711" s="14"/>
       <c r="D711" s="4"/>
       <c r="E711"/>
       <c r="L711" s="7"/>
     </row>
-    <row r="712" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="712" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C712" s="14"/>
       <c r="D712" s="4"/>
       <c r="E712"/>
       <c r="L712" s="7"/>
     </row>
-    <row r="713" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="713" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C713" s="14"/>
       <c r="D713" s="4"/>
       <c r="E713"/>
       <c r="L713" s="7"/>
     </row>
-    <row r="714" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="714" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C714" s="14"/>
       <c r="D714" s="4"/>
       <c r="E714"/>
       <c r="L714" s="7"/>
     </row>
-    <row r="715" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="715" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C715" s="14"/>
       <c r="D715" s="4"/>
       <c r="E715"/>
       <c r="L715" s="7"/>
     </row>
-    <row r="716" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="716" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C716" s="14"/>
       <c r="D716" s="4"/>
       <c r="E716"/>
       <c r="L716" s="7"/>
     </row>
-    <row r="717" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="717" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C717" s="14"/>
       <c r="D717" s="4"/>
       <c r="E717"/>
       <c r="L717" s="7"/>
     </row>
-    <row r="718" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="718" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C718" s="14"/>
       <c r="D718" s="4"/>
       <c r="E718"/>
       <c r="L718" s="7"/>
     </row>
-    <row r="719" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="719" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C719" s="14"/>
       <c r="D719" s="4"/>
       <c r="E719"/>
       <c r="L719" s="7"/>
     </row>
-    <row r="720" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="720" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C720" s="14"/>
       <c r="D720" s="4"/>
       <c r="E720"/>
       <c r="L720" s="7"/>
     </row>
-    <row r="721" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="721" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C721" s="14"/>
       <c r="D721" s="4"/>
       <c r="E721"/>
       <c r="L721" s="7"/>
     </row>
-    <row r="722" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="722" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C722" s="14"/>
       <c r="D722" s="4"/>
       <c r="E722"/>
       <c r="L722" s="7"/>
     </row>
-    <row r="723" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="723" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C723" s="14"/>
       <c r="D723" s="4"/>
       <c r="E723"/>
       <c r="L723" s="7"/>
     </row>
-    <row r="724" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="724" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C724" s="14"/>
       <c r="D724" s="4"/>
       <c r="E724"/>
       <c r="L724" s="7"/>
     </row>
-    <row r="725" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="725" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C725" s="14"/>
       <c r="D725" s="4"/>
       <c r="E725"/>
       <c r="L725" s="7"/>
     </row>
-    <row r="726" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="726" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C726" s="14"/>
       <c r="D726" s="4"/>
       <c r="E726"/>
       <c r="L726" s="7"/>
     </row>
-    <row r="727" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="727" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C727" s="14"/>
       <c r="D727" s="4"/>
       <c r="E727"/>
       <c r="L727" s="7"/>
     </row>
-    <row r="728" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="728" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C728" s="14"/>
       <c r="D728" s="4"/>
       <c r="E728"/>
       <c r="L728" s="7"/>
     </row>
-    <row r="729" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="729" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C729" s="14"/>
       <c r="D729" s="4"/>
       <c r="E729"/>
       <c r="L729" s="7"/>
     </row>
-    <row r="730" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="730" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C730" s="14"/>
       <c r="D730" s="4"/>
       <c r="E730"/>
       <c r="L730" s="7"/>
     </row>
-    <row r="731" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="731" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C731" s="14"/>
       <c r="D731" s="4"/>
       <c r="E731"/>
       <c r="L731" s="7"/>
       <c r="N731" s="16"/>
     </row>
-    <row r="732" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="732" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C732" s="14"/>
       <c r="D732" s="4"/>
       <c r="E732"/>
     </row>
-    <row r="733" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="733" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C733" s="14"/>
       <c r="D733" s="4"/>
       <c r="E733"/>
     </row>
-    <row r="734" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="734" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C734" s="14"/>
       <c r="D734" s="4"/>
       <c r="E734"/>
     </row>
-    <row r="735" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="735" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C735" s="14"/>
       <c r="D735" s="4"/>
       <c r="E735"/>
     </row>
-    <row r="736" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="736" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C736" s="14"/>
       <c r="D736" s="4"/>
       <c r="E736"/>
     </row>
-    <row r="737" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="737" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C737" s="14"/>
       <c r="D737" s="4"/>
       <c r="E737"/>
     </row>
-    <row r="738" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="738" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C738" s="14"/>
       <c r="D738" s="4"/>
       <c r="E738"/>
     </row>
-    <row r="739" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="739" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C739" s="14"/>
       <c r="D739" s="4"/>
       <c r="E739"/>
     </row>
-    <row r="740" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="740" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C740" s="14"/>
       <c r="D740" s="4"/>
       <c r="E740"/>
     </row>
-    <row r="741" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="741" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C741" s="14"/>
       <c r="D741" s="4"/>
       <c r="E741"/>
     </row>
-    <row r="742" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="742" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C742" s="14"/>
       <c r="D742" s="4"/>
       <c r="E742"/>
     </row>
-    <row r="743" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="743" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C743" s="14"/>
       <c r="D743" s="4"/>
       <c r="E743"/>
     </row>
-    <row r="744" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="744" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C744" s="14"/>
       <c r="D744" s="4"/>
       <c r="E744"/>
     </row>
-    <row r="745" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="745" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C745" s="14"/>
       <c r="D745" s="4"/>
       <c r="E745"/>
     </row>
-    <row r="746" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="746" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C746" s="14"/>
       <c r="D746" s="4"/>
       <c r="E746"/>
     </row>
-    <row r="747" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="747" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C747" s="14"/>
       <c r="D747" s="4"/>
       <c r="E747"/>
     </row>
-    <row r="748" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="748" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C748" s="14"/>
       <c r="D748" s="4"/>
       <c r="E748"/>
     </row>
-    <row r="749" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="749" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C749" s="14"/>
       <c r="D749" s="4"/>
       <c r="E749"/>
     </row>
-    <row r="750" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="750" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C750" s="14"/>
       <c r="D750" s="4"/>
       <c r="E750"/>
     </row>
-    <row r="751" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="751" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C751" s="14"/>
       <c r="D751" s="4"/>
       <c r="E751"/>
     </row>
-    <row r="752" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="752" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C752" s="14"/>
       <c r="D752" s="4"/>
       <c r="E752"/>
     </row>
-    <row r="753" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="753" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C753" s="14"/>
       <c r="D753" s="4"/>
       <c r="E753"/>
     </row>
-    <row r="754" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="754" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C754" s="14"/>
       <c r="D754" s="4"/>
       <c r="E754"/>
     </row>
-    <row r="755" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="755" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C755" s="14"/>
       <c r="D755" s="4"/>
       <c r="E755"/>
     </row>
-    <row r="756" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="756" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C756" s="14"/>
       <c r="D756" s="4"/>
       <c r="E756"/>
     </row>
-    <row r="757" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="757" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C757" s="14"/>
       <c r="D757" s="4"/>
       <c r="E757"/>
     </row>
-    <row r="758" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="758" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C758" s="14"/>
       <c r="D758" s="4"/>
       <c r="E758"/>
     </row>
-    <row r="759" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="759" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C759" s="14"/>
       <c r="D759" s="4"/>
       <c r="E759"/>
     </row>
-    <row r="760" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="760" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C760" s="14"/>
       <c r="D760" s="4"/>
       <c r="E760"/>
     </row>
-    <row r="761" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="761" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C761" s="14"/>
       <c r="D761" s="4"/>
       <c r="E761"/>
     </row>
-    <row r="762" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="762" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C762" s="14"/>
       <c r="D762" s="4"/>
       <c r="E762"/>
     </row>
-    <row r="763" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="763" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C763" s="14"/>
       <c r="D763" s="4"/>
       <c r="E763"/>
     </row>
-    <row r="764" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="764" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C764" s="14"/>
       <c r="D764" s="4"/>
       <c r="E764"/>
     </row>
-    <row r="765" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="765" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C765" s="14"/>
       <c r="D765" s="4"/>
       <c r="E765"/>
     </row>
-    <row r="766" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="766" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C766" s="14"/>
       <c r="D766" s="4"/>
       <c r="E766"/>
     </row>
-    <row r="767" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="767" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C767" s="14"/>
       <c r="D767" s="4"/>
       <c r="E767"/>
     </row>
-    <row r="768" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="768" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C768" s="14"/>
       <c r="D768" s="4"/>
       <c r="E768"/>
     </row>
-    <row r="769" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="769" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C769" s="14"/>
       <c r="D769" s="4"/>
       <c r="E769"/>
     </row>
-    <row r="770" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="770" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C770" s="14"/>
       <c r="D770" s="4"/>
       <c r="E770"/>
     </row>
-    <row r="771" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="771" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C771" s="14"/>
       <c r="D771" s="4"/>
       <c r="E771"/>
     </row>
-    <row r="772" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="772" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C772" s="14"/>
       <c r="D772" s="4"/>
       <c r="E772"/>
     </row>
-    <row r="773" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="773" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C773" s="14"/>
       <c r="D773" s="4"/>
       <c r="E773"/>
     </row>
-    <row r="774" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="774" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C774" s="14"/>
       <c r="D774" s="4"/>
       <c r="E774"/>
     </row>
-    <row r="775" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="775" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C775" s="14"/>
       <c r="D775" s="4"/>
       <c r="E775"/>
     </row>
-    <row r="776" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="776" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C776" s="14"/>
       <c r="D776" s="4"/>
       <c r="E776"/>
     </row>
-    <row r="777" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="777" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C777" s="14"/>
       <c r="D777" s="4"/>
       <c r="E777"/>
     </row>
-    <row r="778" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="778" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C778" s="14"/>
       <c r="D778" s="4"/>
       <c r="E778"/>
     </row>
-    <row r="779" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="779" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C779" s="14"/>
       <c r="D779" s="4"/>
       <c r="E779"/>
     </row>
-    <row r="780" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="780" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C780" s="14"/>
       <c r="D780" s="4"/>
       <c r="E780"/>
     </row>
-    <row r="781" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="781" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C781" s="14"/>
       <c r="D781" s="4"/>
       <c r="E781"/>
     </row>
-    <row r="782" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="782" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C782" s="14"/>
       <c r="D782" s="4"/>
       <c r="E782"/>
     </row>
-    <row r="783" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="783" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C783" s="14"/>
       <c r="D783" s="4"/>
       <c r="E783"/>
     </row>
-    <row r="784" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="784" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C784" s="14"/>
       <c r="D784" s="4"/>
       <c r="E784"/>
     </row>
-    <row r="785" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="785" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C785" s="14"/>
       <c r="D785" s="4"/>
       <c r="E785"/>
     </row>
-    <row r="786" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="786" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C786" s="14"/>
       <c r="D786" s="4"/>
       <c r="E786"/>
     </row>
-    <row r="787" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="787" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C787" s="14"/>
       <c r="D787" s="4"/>
       <c r="E787"/>
     </row>
-    <row r="788" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="788" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C788" s="14"/>
       <c r="D788" s="4"/>
       <c r="E788"/>
     </row>
-    <row r="789" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="789" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C789" s="14"/>
       <c r="D789" s="4"/>
       <c r="E789"/>
     </row>
-    <row r="790" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="790" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C790" s="14"/>
       <c r="D790" s="4"/>
       <c r="E790"/>
     </row>
-    <row r="791" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="791" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C791" s="14"/>
       <c r="D791" s="4"/>
       <c r="E791"/>
     </row>
-    <row r="792" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="792" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C792" s="14"/>
       <c r="D792" s="4"/>
       <c r="E792"/>
     </row>
-    <row r="793" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="793" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C793" s="14"/>
       <c r="D793" s="4"/>
       <c r="E793"/>
     </row>
-    <row r="794" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="794" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C794" s="14"/>
       <c r="D794" s="4"/>
       <c r="E794"/>
     </row>
-    <row r="795" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="795" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C795" s="14"/>
       <c r="D795" s="4"/>
       <c r="E795"/>
     </row>
-    <row r="796" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="796" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C796" s="14"/>
       <c r="D796" s="4"/>
       <c r="E796"/>
     </row>
-    <row r="797" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="797" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C797" s="14"/>
       <c r="D797" s="4"/>
       <c r="E797"/>
     </row>
-    <row r="798" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="798" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C798" s="14"/>
       <c r="D798" s="4"/>
       <c r="E798"/>
     </row>
-    <row r="799" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="799" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C799" s="14"/>
       <c r="D799" s="4"/>
       <c r="E799"/>
     </row>
-    <row r="800" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="800" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C800" s="14"/>
       <c r="D800" s="4"/>
       <c r="E800"/>
     </row>
-    <row r="801" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="801" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C801" s="14"/>
       <c r="D801" s="4"/>
       <c r="E801"/>
     </row>
-    <row r="802" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="802" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C802" s="14"/>
       <c r="D802" s="4"/>
       <c r="E802"/>
     </row>
-    <row r="803" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="803" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C803" s="14"/>
       <c r="D803" s="4"/>
       <c r="E803"/>
     </row>
-    <row r="804" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="804" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C804" s="14"/>
       <c r="D804" s="4"/>
       <c r="E804"/>
     </row>
-    <row r="805" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="805" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C805" s="14"/>
       <c r="D805" s="4"/>
       <c r="E805"/>
     </row>
-    <row r="806" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="806" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C806" s="14"/>
       <c r="D806" s="4"/>
       <c r="E806"/>
     </row>
-    <row r="807" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="807" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C807" s="14"/>
       <c r="D807" s="4"/>
       <c r="E807"/>
     </row>
-    <row r="808" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="808" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C808" s="14"/>
       <c r="D808" s="4"/>
       <c r="E808"/>
     </row>
-    <row r="809" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="809" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C809" s="14"/>
       <c r="D809" s="4"/>
       <c r="E809"/>
     </row>
-    <row r="810" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="810" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C810" s="14"/>
       <c r="D810" s="4"/>
       <c r="E810"/>
     </row>
-    <row r="811" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="811" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C811" s="14"/>
       <c r="D811" s="4"/>
       <c r="E811"/>
     </row>
-    <row r="812" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="812" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C812" s="14"/>
       <c r="D812" s="4"/>
       <c r="E812"/>
     </row>
-    <row r="813" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="813" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C813" s="14"/>
       <c r="D813" s="4"/>
       <c r="E813"/>
     </row>
-    <row r="814" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="814" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C814" s="14"/>
       <c r="D814" s="4"/>
       <c r="E814"/>
     </row>
-    <row r="815" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="815" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C815" s="14"/>
       <c r="D815" s="4"/>
       <c r="E815"/>
     </row>
-    <row r="816" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="816" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C816" s="14"/>
       <c r="D816" s="4"/>
       <c r="E816"/>
     </row>
-    <row r="817" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="817" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C817" s="14"/>
       <c r="D817" s="4"/>
       <c r="E817"/>
     </row>
-    <row r="818" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="818" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B818"/>
       <c r="C818" s="14"/>
       <c r="D818" s="4"/>
       <c r="E818"/>
     </row>
-    <row r="819" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="819" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B819"/>
       <c r="C819" s="14"/>
       <c r="D819" s="4"/>
       <c r="E819"/>
     </row>
-    <row r="820" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="820" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B820"/>
       <c r="C820" s="14"/>
       <c r="D820" s="4"/>
       <c r="E820"/>
     </row>
-    <row r="821" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="821" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B821"/>
       <c r="C821" s="14"/>
       <c r="D821" s="4"/>
       <c r="E821"/>
     </row>
-    <row r="822" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="822" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B822"/>
       <c r="C822" s="14"/>
       <c r="D822" s="4"/>
       <c r="E822"/>
     </row>
-    <row r="823" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="823" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B823"/>
       <c r="C823" s="14"/>
       <c r="D823" s="4"/>
       <c r="E823"/>
     </row>
-    <row r="824" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="824" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B824"/>
       <c r="C824" s="14"/>
       <c r="D824" s="4"/>
       <c r="E824"/>
     </row>
-    <row r="825" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="825" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B825"/>
       <c r="C825" s="14"/>
       <c r="D825" s="4"/>
       <c r="E825"/>
     </row>
-    <row r="826" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="826" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B826"/>
       <c r="C826" s="14"/>
       <c r="D826" s="4"/>
       <c r="E826"/>
     </row>
-    <row r="827" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="827" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B827"/>
       <c r="C827" s="14"/>
       <c r="D827" s="4"/>
       <c r="E827"/>
     </row>
-    <row r="828" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="828" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B828"/>
       <c r="C828" s="14"/>
       <c r="D828" s="4"/>
       <c r="E828"/>
     </row>
-    <row r="829" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="829" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B829"/>
       <c r="C829" s="14"/>
       <c r="D829" s="4"/>
       <c r="E829"/>
     </row>
-    <row r="830" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="830" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B830"/>
       <c r="C830" s="14"/>
       <c r="D830" s="4"/>
       <c r="E830"/>
     </row>
-    <row r="831" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="831" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B831"/>
       <c r="C831" s="14"/>
       <c r="D831" s="4"/>
       <c r="E831"/>
     </row>
-    <row r="832" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="832" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B832"/>
       <c r="C832" s="14"/>
       <c r="D832" s="4"/>
       <c r="E832"/>
     </row>
-    <row r="833" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="833" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B833"/>
       <c r="C833" s="14"/>
       <c r="D833" s="4"/>
       <c r="E833"/>
     </row>
-    <row r="834" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="834" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B834"/>
       <c r="C834" s="14"/>
       <c r="D834" s="4"/>
       <c r="E834"/>
     </row>
-    <row r="835" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="835" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B835"/>
       <c r="C835" s="14"/>
       <c r="D835" s="4"/>
       <c r="E835"/>
     </row>
-    <row r="836" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="836" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B836"/>
       <c r="C836" s="14"/>
       <c r="D836" s="4"/>
       <c r="E836"/>
     </row>
-    <row r="837" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="837" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B837"/>
       <c r="C837" s="14"/>
       <c r="D837" s="4"/>
       <c r="E837"/>
     </row>
-    <row r="838" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="838" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B838"/>
       <c r="C838" s="14"/>
       <c r="D838" s="4"/>
       <c r="E838"/>
     </row>
-    <row r="839" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="839" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B839"/>
       <c r="C839" s="14"/>
       <c r="D839" s="4"/>
       <c r="E839"/>
     </row>
-    <row r="840" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="840" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B840"/>
       <c r="C840" s="14"/>
       <c r="D840" s="4"/>
       <c r="E840"/>
     </row>
-    <row r="841" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="841" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B841"/>
       <c r="C841" s="14"/>
       <c r="D841" s="4"/>
       <c r="E841"/>
     </row>
-    <row r="842" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="842" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B842"/>
       <c r="C842" s="14"/>
       <c r="D842" s="4"/>
       <c r="E842"/>
     </row>
-    <row r="843" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="843" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B843"/>
       <c r="C843" s="14"/>
       <c r="D843" s="4"/>
       <c r="E843"/>
     </row>
-    <row r="844" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="844" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B844"/>
       <c r="C844" s="14"/>
       <c r="D844" s="4"/>
       <c r="E844"/>
     </row>
-    <row r="845" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="845" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B845"/>
       <c r="C845" s="14"/>
       <c r="D845" s="4"/>
       <c r="E845"/>
     </row>
-    <row r="846" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="846" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B846"/>
       <c r="C846" s="14"/>
       <c r="D846" s="4"/>
       <c r="E846"/>
     </row>
-    <row r="847" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="847" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B847"/>
       <c r="C847" s="14"/>
       <c r="D847" s="4"/>
       <c r="E847"/>
     </row>
-    <row r="848" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="848" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B848"/>
       <c r="C848" s="14"/>
       <c r="D848" s="4"/>
       <c r="E848"/>
     </row>
-    <row r="849" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="849" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B849"/>
       <c r="C849" s="14"/>
       <c r="D849" s="4"/>
       <c r="E849"/>
     </row>
-    <row r="850" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="850" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B850"/>
       <c r="C850" s="14"/>
       <c r="D850" s="4"/>
       <c r="E850"/>
     </row>
-    <row r="851" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="851" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B851"/>
       <c r="C851" s="14"/>
       <c r="D851" s="4"/>
       <c r="E851"/>
     </row>
-    <row r="852" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="852" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B852"/>
       <c r="C852" s="14"/>
       <c r="D852" s="4"/>
       <c r="E852"/>
     </row>
-    <row r="853" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="853" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B853"/>
       <c r="C853" s="14"/>
       <c r="D853" s="4"/>
       <c r="E853"/>
     </row>
-    <row r="854" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="854" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B854"/>
       <c r="C854" s="14"/>
       <c r="D854" s="4"/>
       <c r="E854"/>
     </row>
-    <row r="855" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="855" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B855"/>
       <c r="C855" s="14"/>
       <c r="D855" s="4"/>
       <c r="E855"/>
     </row>
-    <row r="856" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="856" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B856"/>
       <c r="C856" s="14"/>
       <c r="D856" s="4"/>
       <c r="E856"/>
     </row>
-    <row r="857" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="857" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B857"/>
       <c r="C857" s="14"/>
       <c r="D857" s="4"/>
       <c r="E857"/>
     </row>
-    <row r="858" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="858" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B858"/>
       <c r="C858" s="14"/>
       <c r="D858" s="4"/>
       <c r="E858"/>
     </row>
-    <row r="859" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="859" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B859"/>
       <c r="C859" s="14"/>
       <c r="D859" s="4"/>
       <c r="E859"/>
     </row>
-    <row r="860" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="860" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B860"/>
       <c r="C860" s="14"/>
       <c r="D860" s="4"/>
       <c r="E860"/>
     </row>
-    <row r="861" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="861" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B861"/>
       <c r="C861" s="14"/>
       <c r="D861" s="4"/>
       <c r="E861"/>
     </row>
-    <row r="862" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="862" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B862"/>
       <c r="C862" s="14"/>
       <c r="D862" s="4"/>
       <c r="E862"/>
     </row>
-    <row r="863" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="863" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B863"/>
       <c r="C863" s="14"/>
       <c r="D863" s="4"/>
       <c r="E863"/>
     </row>
-    <row r="864" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="864" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B864"/>
       <c r="C864" s="14"/>
       <c r="D864" s="4"/>
       <c r="E864"/>
     </row>
-    <row r="865" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="865" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B865"/>
       <c r="C865" s="14"/>
       <c r="D865" s="4"/>
       <c r="E865"/>
     </row>
-    <row r="866" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="866" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B866"/>
       <c r="C866" s="14"/>
       <c r="D866" s="4"/>
       <c r="E866"/>
     </row>
-    <row r="867" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="867" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B867"/>
       <c r="C867" s="14"/>
       <c r="D867" s="4"/>
       <c r="E867"/>
     </row>
-    <row r="868" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="868" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B868"/>
       <c r="C868" s="14"/>
       <c r="D868" s="4"/>
       <c r="E868"/>
     </row>
-    <row r="869" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="869" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B869"/>
       <c r="C869" s="14"/>
       <c r="D869" s="4"/>
       <c r="E869"/>
     </row>
-    <row r="870" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="870" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B870"/>
       <c r="C870" s="14"/>
       <c r="D870" s="4"/>
       <c r="E870"/>
     </row>
-    <row r="871" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="871" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B871"/>
       <c r="C871" s="14"/>
       <c r="D871" s="4"/>
       <c r="E871"/>
     </row>
-    <row r="872" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="872" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B872"/>
       <c r="C872" s="14"/>
       <c r="D872" s="4"/>
       <c r="E872"/>
     </row>
-    <row r="873" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="873" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B873"/>
       <c r="C873" s="14"/>
       <c r="D873" s="4"/>
       <c r="E873"/>
     </row>
-    <row r="874" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="874" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B874"/>
       <c r="C874" s="14"/>
       <c r="D874" s="4"/>
       <c r="E874"/>
     </row>
-    <row r="875" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="875" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B875"/>
       <c r="C875" s="14"/>
       <c r="D875" s="4"/>
       <c r="E875"/>
     </row>
-    <row r="876" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="876" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B876"/>
       <c r="C876" s="14"/>
       <c r="D876" s="4"/>
       <c r="E876"/>
     </row>
-    <row r="877" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="877" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B877"/>
       <c r="C877" s="14"/>
       <c r="D877" s="4"/>
       <c r="E877"/>
     </row>
-    <row r="878" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="878" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B878"/>
       <c r="C878" s="14"/>
       <c r="D878" s="4"/>
       <c r="E878"/>
     </row>
-    <row r="879" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="879" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B879"/>
       <c r="C879" s="14"/>
       <c r="D879" s="4"/>
       <c r="E879"/>
     </row>
-    <row r="880" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="880" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B880"/>
       <c r="C880" s="14"/>
       <c r="D880" s="4"/>
       <c r="E880"/>
     </row>
-    <row r="881" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="881" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B881"/>
       <c r="C881" s="14"/>
       <c r="D881" s="4"/>
       <c r="E881"/>
     </row>
-    <row r="882" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="882" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B882"/>
       <c r="C882" s="14"/>
       <c r="D882" s="4"/>
       <c r="E882"/>
     </row>
-    <row r="883" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="883" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B883"/>
       <c r="C883" s="14"/>
       <c r="D883" s="4"/>
       <c r="E883"/>
     </row>
-    <row r="884" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="884" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B884"/>
       <c r="C884" s="14"/>
       <c r="D884" s="4"/>
       <c r="E884"/>
     </row>
-    <row r="885" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="885" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B885"/>
       <c r="C885" s="14"/>
       <c r="D885" s="4"/>
       <c r="E885"/>
     </row>
-    <row r="886" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="886" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B886"/>
       <c r="C886" s="14"/>
       <c r="D886" s="4"/>
       <c r="E886"/>
     </row>
-    <row r="887" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="887" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B887"/>
       <c r="C887" s="14"/>
       <c r="D887" s="4"/>
       <c r="E887"/>
     </row>
-    <row r="888" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="888" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B888"/>
       <c r="C888" s="14"/>
       <c r="D888" s="4"/>
       <c r="E888"/>
     </row>
-    <row r="889" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="889" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B889"/>
       <c r="C889" s="14"/>
       <c r="D889" s="4"/>
       <c r="E889"/>
     </row>
-    <row r="890" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="890" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B890"/>
       <c r="C890" s="14"/>
       <c r="D890" s="4"/>
       <c r="E890"/>
     </row>
-    <row r="891" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="891" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B891"/>
       <c r="C891" s="14"/>
       <c r="D891" s="4"/>
       <c r="E891"/>
     </row>
-    <row r="892" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="892" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B892"/>
       <c r="C892" s="14"/>
       <c r="D892" s="4"/>
       <c r="E892"/>
     </row>
-    <row r="893" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="893" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B893"/>
       <c r="C893" s="14"/>
       <c r="D893" s="4"/>
       <c r="E893"/>
     </row>
-    <row r="894" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="894" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B894"/>
       <c r="C894" s="14"/>
       <c r="D894" s="4"/>
       <c r="E894"/>
     </row>
-    <row r="895" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="895" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B895"/>
       <c r="C895" s="14"/>
       <c r="D895" s="4"/>
       <c r="E895"/>
     </row>
-    <row r="896" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="896" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B896"/>
       <c r="C896" s="14"/>
       <c r="D896" s="4"/>
       <c r="E896"/>
     </row>
-    <row r="897" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="897" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B897"/>
       <c r="C897" s="14"/>
       <c r="D897" s="4"/>
       <c r="E897"/>
     </row>
-    <row r="898" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="898" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B898"/>
       <c r="C898" s="14"/>
       <c r="D898" s="4"/>
       <c r="E898"/>
     </row>
-    <row r="899" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="899" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B899"/>
       <c r="C899" s="14"/>
       <c r="D899" s="4"/>
       <c r="E899"/>
     </row>
-    <row r="900" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="900" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B900"/>
       <c r="C900" s="14"/>
       <c r="D900" s="4"/>
       <c r="E900"/>
     </row>
-    <row r="901" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="901" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B901"/>
       <c r="C901" s="14"/>
       <c r="D901" s="4"/>
       <c r="E901"/>
     </row>
-    <row r="902" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="902" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B902"/>
       <c r="C902" s="14"/>
       <c r="D902" s="4"/>
       <c r="E902"/>
     </row>
-    <row r="903" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="903" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B903"/>
       <c r="C903" s="14"/>
       <c r="D903" s="4"/>
       <c r="E903"/>
     </row>
-    <row r="904" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="904" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B904"/>
       <c r="C904" s="14"/>
       <c r="D904" s="4"/>
       <c r="E904"/>
     </row>
-    <row r="905" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="905" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B905"/>
       <c r="C905" s="14"/>
       <c r="D905" s="4"/>
       <c r="E905"/>
     </row>
-    <row r="906" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="906" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B906"/>
       <c r="C906" s="14"/>
       <c r="D906" s="4"/>
       <c r="E906"/>
     </row>
-    <row r="907" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="907" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B907"/>
       <c r="C907" s="14"/>
       <c r="D907" s="4"/>
       <c r="E907"/>
     </row>
-    <row r="908" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="908" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B908"/>
       <c r="C908" s="14"/>
       <c r="D908" s="4"/>
       <c r="E908"/>
     </row>
-    <row r="909" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="909" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B909"/>
       <c r="C909" s="14"/>
       <c r="D909" s="4"/>
       <c r="E909"/>
     </row>
-    <row r="910" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="910" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B910"/>
       <c r="C910" s="14"/>
       <c r="D910" s="4"/>
       <c r="E910"/>
     </row>
-    <row r="911" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="911" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B911"/>
       <c r="C911" s="14"/>
       <c r="D911" s="4"/>
       <c r="E911"/>
     </row>
-    <row r="912" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="912" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B912"/>
       <c r="C912" s="14"/>
       <c r="D912" s="4"/>
       <c r="E912"/>
     </row>
-    <row r="913" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="913" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B913"/>
       <c r="C913" s="14"/>
       <c r="D913" s="4"/>
       <c r="E913"/>
     </row>
-    <row r="914" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="914" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B914"/>
       <c r="C914" s="14"/>
       <c r="D914" s="4"/>
       <c r="E914"/>
     </row>
-    <row r="915" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="915" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B915"/>
       <c r="C915" s="14"/>
       <c r="D915" s="4"/>
       <c r="E915"/>
     </row>
-    <row r="916" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="916" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B916"/>
       <c r="C916" s="14"/>
       <c r="D916" s="4"/>
       <c r="E916"/>
     </row>
-    <row r="917" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="917" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B917"/>
       <c r="C917" s="14"/>
       <c r="D917" s="4"/>
       <c r="E917"/>
     </row>
-    <row r="918" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="918" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B918"/>
       <c r="C918" s="14"/>
       <c r="D918" s="4"/>
       <c r="E918"/>
     </row>
-    <row r="919" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="919" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B919"/>
       <c r="C919" s="14"/>
       <c r="D919" s="4"/>
       <c r="E919"/>
     </row>
-    <row r="920" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="920" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B920"/>
       <c r="C920" s="14"/>
       <c r="D920" s="4"/>
       <c r="E920"/>
     </row>
-    <row r="921" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="921" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B921"/>
       <c r="C921" s="14"/>
       <c r="D921" s="4"/>
       <c r="E921"/>
     </row>
-    <row r="922" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="922" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B922"/>
       <c r="C922" s="14"/>
       <c r="D922" s="4"/>
       <c r="E922"/>
     </row>
-    <row r="923" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="923" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B923"/>
       <c r="C923" s="14"/>
       <c r="D923" s="4"/>
       <c r="E923"/>
     </row>
-    <row r="924" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="924" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B924"/>
       <c r="C924" s="14"/>
       <c r="D924" s="4"/>
       <c r="E924"/>
     </row>
-    <row r="925" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="925" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B925"/>
       <c r="C925" s="14"/>
       <c r="D925" s="4"/>
       <c r="E925"/>
     </row>
-    <row r="926" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="926" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B926"/>
       <c r="C926" s="14"/>
       <c r="D926" s="4"/>
       <c r="E926"/>
     </row>
-    <row r="927" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="927" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B927"/>
       <c r="C927" s="14"/>
       <c r="D927" s="4"/>
       <c r="E927"/>
     </row>
-    <row r="928" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="928" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B928"/>
       <c r="C928" s="14"/>
       <c r="D928" s="4"/>
       <c r="E928"/>
     </row>
-    <row r="929" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="929" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B929"/>
       <c r="C929" s="14"/>
       <c r="D929" s="4"/>
       <c r="E929"/>
     </row>
-    <row r="930" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="930" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B930"/>
       <c r="C930" s="14"/>
       <c r="D930" s="4"/>
       <c r="E930"/>
     </row>
-    <row r="931" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="931" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B931"/>
       <c r="C931" s="14"/>
       <c r="D931" s="4"/>
       <c r="E931"/>
     </row>
-    <row r="932" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="932" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B932"/>
       <c r="C932" s="14"/>
       <c r="D932" s="4"/>
       <c r="E932"/>
     </row>
-    <row r="933" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="933" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B933"/>
       <c r="C933" s="14"/>
       <c r="D933" s="4"/>
       <c r="E933"/>
     </row>
-    <row r="934" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="934" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B934"/>
       <c r="C934" s="14"/>
       <c r="D934" s="4"/>
       <c r="E934"/>
     </row>
-    <row r="935" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="935" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B935"/>
       <c r="C935" s="14"/>
       <c r="D935" s="4"/>
       <c r="E935"/>
     </row>
-    <row r="936" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="936" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B936"/>
       <c r="C936" s="14"/>
       <c r="D936" s="4"/>
       <c r="E936"/>
     </row>
-    <row r="937" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="937" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B937"/>
       <c r="C937" s="14"/>
       <c r="D937" s="4"/>
       <c r="E937"/>
     </row>
-    <row r="938" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="938" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B938"/>
       <c r="C938" s="14"/>
       <c r="D938" s="4"/>
       <c r="E938"/>
     </row>
-    <row r="939" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="939" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B939"/>
       <c r="C939" s="14"/>
       <c r="D939" s="4"/>
       <c r="E939"/>
     </row>
-    <row r="940" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="940" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B940"/>
       <c r="C940" s="14"/>
       <c r="D940" s="4"/>
       <c r="E940"/>
     </row>
-    <row r="941" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="941" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B941"/>
       <c r="C941" s="14"/>
       <c r="D941" s="4"/>
       <c r="E941"/>
     </row>
-    <row r="942" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="942" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B942"/>
       <c r="C942" s="14"/>
       <c r="D942" s="4"/>
       <c r="E942"/>
     </row>
-    <row r="943" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="943" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B943"/>
       <c r="C943" s="14"/>
       <c r="D943" s="4"/>
       <c r="E943"/>
     </row>
-    <row r="944" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="944" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B944"/>
       <c r="C944" s="14"/>
       <c r="D944" s="4"/>
       <c r="E944"/>
     </row>
-    <row r="945" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="945" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B945"/>
       <c r="C945" s="14"/>
       <c r="D945" s="4"/>
       <c r="E945"/>
     </row>
-    <row r="946" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="946" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B946"/>
       <c r="C946" s="14"/>
       <c r="D946" s="4"/>
       <c r="E946"/>
     </row>
-    <row r="947" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="947" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B947"/>
       <c r="C947" s="14"/>
       <c r="D947" s="4"/>
       <c r="E947"/>
     </row>
-    <row r="948" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="948" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B948"/>
       <c r="C948" s="14"/>
       <c r="D948" s="4"/>
       <c r="E948"/>
     </row>
-    <row r="949" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="949" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B949"/>
       <c r="C949" s="14"/>
       <c r="D949" s="4"/>
       <c r="E949"/>
     </row>
-    <row r="950" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="950" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B950"/>
       <c r="C950" s="14"/>
       <c r="D950" s="4"/>
       <c r="E950"/>
     </row>
-    <row r="951" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="951" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B951"/>
       <c r="C951" s="14"/>
       <c r="D951" s="4"/>
       <c r="E951"/>
     </row>
-    <row r="952" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="952" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B952"/>
       <c r="C952" s="14"/>
       <c r="D952" s="4"/>
       <c r="E952"/>
     </row>
-    <row r="953" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="953" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B953"/>
       <c r="C953" s="14"/>
       <c r="D953" s="4"/>
       <c r="E953"/>
     </row>
-    <row r="954" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="954" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B954"/>
       <c r="C954" s="14"/>
       <c r="D954" s="4"/>
       <c r="E954"/>
     </row>
-    <row r="955" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="955" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B955"/>
       <c r="C955" s="14"/>
       <c r="D955" s="4"/>
       <c r="E955"/>
     </row>
-    <row r="956" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="956" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B956"/>
       <c r="C956" s="14"/>
       <c r="D956" s="4"/>
       <c r="E956"/>
     </row>
-    <row r="957" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="957" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B957"/>
       <c r="C957" s="14"/>
       <c r="D957" s="4"/>
       <c r="E957"/>
     </row>
-    <row r="958" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="958" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B958"/>
       <c r="C958" s="14"/>
       <c r="D958" s="4"/>
       <c r="E958"/>
     </row>
-    <row r="959" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="959" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B959"/>
       <c r="C959" s="14"/>
       <c r="D959" s="4"/>
       <c r="E959"/>
     </row>
-    <row r="960" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="960" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B960"/>
       <c r="C960" s="14"/>
       <c r="D960" s="4"/>
       <c r="E960"/>
     </row>
-    <row r="961" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="961" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B961"/>
       <c r="C961" s="14"/>
       <c r="D961" s="4"/>
       <c r="E961"/>
     </row>
-    <row r="962" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="962" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B962"/>
       <c r="C962" s="14"/>
       <c r="D962" s="4"/>
       <c r="E962"/>
     </row>
-    <row r="963" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="963" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B963"/>
       <c r="C963" s="14"/>
       <c r="D963" s="4"/>
       <c r="E963"/>
     </row>
-    <row r="964" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="964" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B964"/>
       <c r="C964" s="14"/>
       <c r="D964" s="4"/>
       <c r="E964"/>
     </row>
-    <row r="965" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="965" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B965"/>
       <c r="C965" s="14"/>
       <c r="D965" s="4"/>
       <c r="E965"/>
     </row>
-    <row r="966" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="966" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B966"/>
       <c r="C966" s="14"/>
       <c r="D966" s="4"/>
       <c r="E966"/>
     </row>
-    <row r="967" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="967" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B967"/>
       <c r="C967" s="14"/>
       <c r="D967" s="4"/>
       <c r="E967"/>
     </row>
-    <row r="968" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="968" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B968"/>
       <c r="C968" s="14"/>
       <c r="D968" s="4"/>
       <c r="E968"/>
     </row>
-    <row r="969" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="969" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B969"/>
       <c r="C969" s="14"/>
       <c r="D969" s="4"/>
       <c r="E969"/>
     </row>
-    <row r="970" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="970" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B970"/>
       <c r="C970" s="14"/>
       <c r="D970" s="4"/>
       <c r="E970"/>
     </row>
-    <row r="971" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="971" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B971"/>
       <c r="C971" s="14"/>
       <c r="D971" s="4"/>
       <c r="E971"/>
     </row>
-    <row r="972" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="972" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B972"/>
       <c r="C972" s="14"/>
       <c r="D972" s="4"/>
       <c r="E972"/>
     </row>
-    <row r="973" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="973" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B973"/>
       <c r="C973" s="14"/>
       <c r="D973" s="4"/>
       <c r="E973"/>
     </row>
-    <row r="974" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="974" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B974"/>
       <c r="C974" s="14"/>
       <c r="D974" s="4"/>
       <c r="E974"/>
     </row>
-    <row r="975" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="975" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B975"/>
       <c r="C975" s="14"/>
       <c r="D975" s="4"/>
       <c r="E975"/>
     </row>
-    <row r="976" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="976" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B976"/>
       <c r="C976" s="14"/>
       <c r="D976" s="4"/>
       <c r="E976"/>
     </row>
-    <row r="977" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="977" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B977"/>
       <c r="C977" s="14"/>
       <c r="D977" s="4"/>
       <c r="E977"/>
     </row>
-    <row r="978" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="978" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B978"/>
       <c r="C978" s="14"/>
       <c r="D978" s="4"/>
       <c r="E978"/>
     </row>
-    <row r="979" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="979" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B979"/>
       <c r="C979" s="14"/>
       <c r="D979" s="4"/>
       <c r="E979"/>
     </row>
-    <row r="980" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="980" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B980"/>
       <c r="C980" s="14"/>
       <c r="D980" s="4"/>
       <c r="E980"/>
     </row>
-    <row r="981" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="981" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B981"/>
       <c r="C981" s="14"/>
       <c r="D981" s="4"/>
       <c r="E981"/>
     </row>
-    <row r="982" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="982" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B982"/>
       <c r="C982" s="14"/>
       <c r="D982" s="4"/>
       <c r="E982"/>
     </row>
-    <row r="983" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="983" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B983"/>
       <c r="C983" s="14"/>
       <c r="D983" s="4"/>
       <c r="E983"/>
     </row>
-    <row r="984" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="984" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B984"/>
       <c r="C984" s="14"/>
       <c r="D984" s="4"/>
       <c r="E984"/>
     </row>
-    <row r="985" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="985" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B985"/>
       <c r="C985" s="14"/>
       <c r="D985" s="4"/>
       <c r="E985"/>
     </row>
-    <row r="986" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="986" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B986"/>
       <c r="C986" s="14"/>
       <c r="D986" s="4"/>
       <c r="E986"/>
     </row>
-    <row r="987" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="987" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B987"/>
       <c r="C987" s="14"/>
       <c r="D987" s="4"/>
       <c r="E987"/>
     </row>
-    <row r="988" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="988" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B988"/>
       <c r="C988" s="14"/>
       <c r="D988" s="4"/>
       <c r="E988"/>
     </row>
-    <row r="989" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="989" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B989"/>
       <c r="C989" s="14"/>
       <c r="D989" s="4"/>
       <c r="E989"/>
     </row>
-    <row r="990" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="990" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B990"/>
       <c r="C990" s="14"/>
       <c r="D990" s="4"/>
       <c r="E990"/>
     </row>
-    <row r="991" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="991" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B991"/>
       <c r="C991" s="14"/>
       <c r="D991" s="4"/>
       <c r="E991"/>
     </row>
-    <row r="992" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="992" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B992"/>
       <c r="C992" s="14"/>
       <c r="D992" s="4"/>
@@ -11116,15 +11192,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3014846-D0FF-4112-9D8F-8E8A4AA4D994}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="47.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="47.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>29</v>
       </c>
@@ -11144,7 +11220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -11153,7 +11229,7 @@
       </c>
       <c r="D2" s="9"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -11173,7 +11249,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>57</v>
       </c>
@@ -11193,7 +11269,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -11213,7 +11289,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -11233,7 +11309,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -11253,7 +11329,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>57</v>
       </c>
@@ -11273,7 +11349,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>57</v>
       </c>
@@ -11293,7 +11369,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>57</v>
       </c>
@@ -11313,7 +11389,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>29</v>
       </c>
@@ -11333,7 +11409,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -11353,7 +11429,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -11373,7 +11449,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -11393,7 +11469,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -11413,7 +11489,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -11433,7 +11509,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>19</v>
       </c>
@@ -11450,7 +11526,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -11470,7 +11546,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -11490,29 +11566,29 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C27" s="8"/>
       <c r="D27" s="17"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D28" s="17"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D29" s="17"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D30" s="17"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D31" s="17"/>
     </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D33" s="6"/>
     </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D34" s="17"/>
     </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D35" s="17"/>
     </row>
   </sheetData>
@@ -11528,29 +11604,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C07B8FD-7D60-4BE0-84C7-595BF0B6409D}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:T9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.5" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" customWidth="1"/>
-    <col min="4" max="4" width="34.5" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
-    <col min="6" max="6" width="17.83203125" customWidth="1"/>
-    <col min="7" max="7" width="30.83203125" customWidth="1"/>
-    <col min="8" max="8" width="21.5" customWidth="1"/>
-    <col min="9" max="10" width="17.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="34.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="30.85546875" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" customWidth="1"/>
+    <col min="9" max="10" width="17.85546875" customWidth="1"/>
     <col min="11" max="11" width="19" customWidth="1"/>
-    <col min="12" max="12" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.83203125" customWidth="1"/>
+    <col min="12" max="12" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" customWidth="1"/>
     <col min="14" max="14" width="15" customWidth="1"/>
-    <col min="15" max="15" width="19.6640625" customWidth="1"/>
-    <col min="16" max="16" width="32.1640625" customWidth="1"/>
-    <col min="17" max="17" width="79.33203125" customWidth="1"/>
-    <col min="18" max="18" width="124.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="32.5" customWidth="1"/>
-    <col min="20" max="20" width="30.33203125" customWidth="1"/>
+    <col min="15" max="15" width="19.7109375" customWidth="1"/>
+    <col min="16" max="16" width="32.140625" customWidth="1"/>
+    <col min="17" max="17" width="79.28515625" customWidth="1"/>
+    <col min="18" max="18" width="124.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="32.42578125" customWidth="1"/>
+    <col min="20" max="20" width="30.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>33</v>
       </c>
@@ -11612,7 +11688,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -11677,7 +11753,7 @@
         <v>examplePBPCommon.email@example.com</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -11742,7 +11818,72 @@
         <v>examplePBPCommon.email@example.com</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="M4" s="27">
+        <v>45658</v>
+      </c>
+      <c r="N4" s="28">
+        <v>45658</v>
+      </c>
+      <c r="O4" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="P4" s="29" t="str">
+        <f>T_CustomerMasterdata[[#This Row],[Customer ref. SAP]]&amp;T_CustomerMasterdata[[#This Row],[Effective]]&amp;T_CustomerMasterdata[[#This Row],[Mailing date]]&amp;T_CustomerMasterdata[[#This Row],[Last Price List Version]]</f>
+        <v>XXXXX34565845658V1</v>
+      </c>
+      <c r="Q4" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="R4" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="S4" s="31" t="str">
+        <f>V_Email_PBPCostingManager</f>
+        <v>internalpersonPBP@internal.com</v>
+      </c>
+      <c r="T4" s="24" t="str">
+        <f>V_Email_PBPCommon</f>
+        <v>examplePBPCommon.email@example.com</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="5"/>
@@ -11753,10 +11894,14 @@
     <hyperlink ref="R3" r:id="rId2" xr:uid="{A609A81C-0F4A-CB49-9F7D-FD4BD488EAC7}"/>
     <hyperlink ref="S2" r:id="rId3" display="internalpersonPBP@internal.com;" xr:uid="{A6DFDDCD-A2EC-9E4D-96BD-CB8F5C4BB81B}"/>
     <hyperlink ref="S3" r:id="rId4" display="internalpersonPBP@internal.com;" xr:uid="{F0288076-0AEA-D243-B2C5-68D2889F5B4B}"/>
+    <hyperlink ref="Q4" r:id="rId5" xr:uid="{07D83331-DCC0-4AAF-AED4-215CA08AA06E}"/>
+    <hyperlink ref="R4" r:id="rId6" xr:uid="{38B989C7-7519-4B9D-9B7D-BCCD210208D0}"/>
+    <hyperlink ref="S4" r:id="rId7" display="internalpersonPBP@internal.com;" xr:uid="{1C9A4A9B-9597-45CE-A5CA-F741E7D486CF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId8"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>
@@ -11764,13 +11909,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{205B7575-87E9-1E48-84E5-FF5A99EC1C43}">
   <dimension ref="A1:N46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11808,7 +11953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>11</v>
       </c>
@@ -11846,7 +11991,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>11</v>
       </c>
@@ -11884,7 +12029,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
         <v>11</v>
       </c>
@@ -11922,7 +12067,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>11</v>
       </c>
@@ -11960,7 +12105,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>11</v>
       </c>
@@ -11998,7 +12143,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>11</v>
       </c>
@@ -12036,7 +12181,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
         <v>11</v>
       </c>
@@ -12074,7 +12219,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>11</v>
       </c>
@@ -12112,7 +12257,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>11</v>
       </c>
@@ -12150,7 +12295,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
         <v>11</v>
       </c>
@@ -12188,7 +12333,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>11</v>
       </c>
@@ -12226,7 +12371,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>11</v>
       </c>
@@ -12246,7 +12391,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
         <v>11</v>
       </c>
@@ -12266,7 +12411,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
         <v>12</v>
       </c>
@@ -12286,7 +12431,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
         <v>12</v>
       </c>
@@ -12306,7 +12451,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>12</v>
       </c>
@@ -12326,7 +12471,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
         <v>12</v>
       </c>
@@ -12346,7 +12491,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
         <v>31</v>
       </c>
@@ -12366,7 +12511,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
         <v>31</v>
       </c>
@@ -12386,7 +12531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
         <v>31</v>
       </c>
@@ -12406,7 +12551,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>31</v>
       </c>
@@ -12426,7 +12571,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
         <v>31</v>
       </c>
@@ -12446,7 +12591,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>13</v>
       </c>
@@ -12466,7 +12611,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
         <v>13</v>
       </c>
@@ -12486,7 +12631,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
         <v>13</v>
       </c>
@@ -12506,7 +12651,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
         <v>13</v>
       </c>
@@ -12526,7 +12671,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="20" t="s">
         <v>13</v>
       </c>
@@ -12546,7 +12691,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
         <v>13</v>
       </c>
@@ -12566,7 +12711,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="20" t="s">
         <v>13</v>
       </c>
@@ -12586,7 +12731,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
         <v>13</v>
       </c>
@@ -12606,7 +12751,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
         <v>13</v>
       </c>
@@ -12626,7 +12771,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
         <v>13</v>
       </c>
@@ -12646,7 +12791,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
         <v>13</v>
       </c>
@@ -12666,7 +12811,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
         <v>13</v>
       </c>
@@ -12686,7 +12831,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="20" t="s">
         <v>13</v>
       </c>
@@ -12706,7 +12851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="20" t="s">
         <v>13</v>
       </c>
@@ -12726,7 +12871,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
         <v>13</v>
       </c>
@@ -12746,7 +12891,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="20" t="s">
         <v>13</v>
       </c>
@@ -12766,7 +12911,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="20" t="s">
         <v>14</v>
       </c>
@@ -12786,7 +12931,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="20" t="s">
         <v>14</v>
       </c>
@@ -12806,7 +12951,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="20" t="s">
         <v>14</v>
       </c>
@@ -12826,7 +12971,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="20" t="s">
         <v>14</v>
       </c>
@@ -12846,7 +12991,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="20" t="s">
         <v>14</v>
       </c>
@@ -12866,7 +13011,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="20" t="s">
         <v>14</v>
       </c>
@@ -12886,7 +13031,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="20" t="s">
         <v>14</v>
       </c>
@@ -12918,14 +13063,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1954576B-4B89-2B4C-B69F-04B690094127}">
   <dimension ref="A1:D46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
@@ -12939,7 +13084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>11</v>
       </c>
@@ -12950,7 +13095,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
@@ -12961,7 +13106,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>11</v>
       </c>
@@ -12972,7 +13117,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>11</v>
       </c>
@@ -12983,7 +13128,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>11</v>
       </c>
@@ -12994,7 +13139,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>11</v>
       </c>
@@ -13005,7 +13150,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>11</v>
       </c>
@@ -13016,7 +13161,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>11</v>
       </c>
@@ -13027,7 +13172,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>11</v>
       </c>
@@ -13038,7 +13183,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>11</v>
       </c>
@@ -13049,7 +13194,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>11</v>
       </c>
@@ -13060,7 +13205,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>11</v>
       </c>
@@ -13071,7 +13216,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>11</v>
       </c>
@@ -13082,7 +13227,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>12</v>
       </c>
@@ -13093,7 +13238,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>12</v>
       </c>
@@ -13104,7 +13249,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>12</v>
       </c>
@@ -13115,7 +13260,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>12</v>
       </c>
@@ -13126,7 +13271,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>31</v>
       </c>
@@ -13137,7 +13282,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>31</v>
       </c>
@@ -13148,7 +13293,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>31</v>
       </c>
@@ -13159,7 +13304,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>31</v>
       </c>
@@ -13170,7 +13315,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>31</v>
       </c>
@@ -13181,7 +13326,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>13</v>
       </c>
@@ -13192,7 +13337,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>13</v>
       </c>
@@ -13203,7 +13348,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>13</v>
       </c>
@@ -13214,7 +13359,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>13</v>
       </c>
@@ -13225,7 +13370,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>13</v>
       </c>
@@ -13236,7 +13381,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>13</v>
       </c>
@@ -13247,7 +13392,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>13</v>
       </c>
@@ -13258,7 +13403,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>13</v>
       </c>
@@ -13269,7 +13414,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>13</v>
       </c>
@@ -13280,7 +13425,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>13</v>
       </c>
@@ -13291,7 +13436,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>13</v>
       </c>
@@ -13302,7 +13447,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>13</v>
       </c>
@@ -13313,7 +13458,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>13</v>
       </c>
@@ -13324,7 +13469,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>13</v>
       </c>
@@ -13335,7 +13480,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>13</v>
       </c>
@@ -13346,7 +13491,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>13</v>
       </c>
@@ -13357,7 +13502,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>14</v>
       </c>
@@ -13368,7 +13513,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>14</v>
       </c>
@@ -13379,7 +13524,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>14</v>
       </c>
@@ -13390,7 +13535,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>14</v>
       </c>
@@ -13401,7 +13546,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>14</v>
       </c>
@@ -13412,7 +13557,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>14</v>
       </c>
@@ -13423,7 +13568,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>14</v>
       </c>
@@ -13476,6 +13621,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007F85B960C90A7443AE9769C1277710FF" ma:contentTypeVersion="36" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba1ec58bf0b30ed83898e540bcef4168">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xmlns:ns3="7e83e573-fb93-452c-9f3b-7b87af48cc96" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c72d53073e6a1b4c183bb84394528e2c" ns2:_="" ns3:_="">
     <xsd:import namespace="dc163805-5a8a-4bac-b0c0-60a9bfcd087a"/>
@@ -17159,15 +17313,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F55DE33-C1A5-4F20-B814-5EC50C36FAFB}">
   <ds:schemaRefs>
@@ -17180,6 +17325,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08C24CE9-94B3-4210-8D15-1D41A580968E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F210950-82D4-49BA-967C-8DE6F1311AF0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17198,14 +17351,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08C24CE9-94B3-4210-8D15-1D41A580968E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{329e91b0-e21f-48fb-a071-456717ecc28e}" enabled="0" method="" siteId="{329e91b0-e21f-48fb-a071-456717ecc28e}" removed="1"/>
